--- a/Documents/Actividades realizadas/ActividadesN__.xlsx
+++ b/Documents/Actividades realizadas/ActividadesN__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\1.- VioletaSystem\Documents\Actividades realizadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09807BA6-07F8-447D-B203-C2D889F5EE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DDC944-032F-48EC-ADE9-ABD6600F64C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HORAS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="347">
   <si>
     <t>Descripción</t>
   </si>
@@ -1030,6 +1030,54 @@
   </si>
   <si>
     <t>Reunión mostrando el avance de taller</t>
+  </si>
+  <si>
+    <t>Calculo de los costos y precios de venta en la pantalla de tipos de cambios</t>
+  </si>
+  <si>
+    <t>Backend: endpoint para insertar o actualizar registro de firma por status de taller</t>
+  </si>
+  <si>
+    <t>Frontend: apertura de cámara, captura de foto y cambio entre cámara frontal/trasera en modal de imágenes del encabezado</t>
+  </si>
+  <si>
+    <t>Frontend: misma funcionalidad de cámara replicada en modal de imágenes del activo del cliente</t>
+  </si>
+  <si>
+    <t>Backend: endpoint para obtener historial completo de firmas con JOINs a usuarios y tablas de catálogo</t>
+  </si>
+  <si>
+    <t>Backend: extracción de firma activa como subquery independiente del SELECT principal del taller</t>
+  </si>
+  <si>
+    <t>Frontend: modal de firma con opciones Aprobar, Rechazar y No firmar, con comentario requerido al rechazar</t>
+  </si>
+  <si>
+    <t>Frontend: modal de historial de firmas con tarjetas por registro, íconos y colores por estado</t>
+  </si>
+  <si>
+    <t>Frontend: métodos en taller.component.ts para insertar firma al cambiar status y abrir ambos modales</t>
+  </si>
+  <si>
+    <t>Frontend: reestructura del encabezado sticky del taller con tarjeta de estado de firma centrada</t>
+  </si>
+  <si>
+    <t>Frontend: botones Re-Asignar, Re-Finalizar y Re-Entregar cuando la firma fue rechazada</t>
+  </si>
+  <si>
+    <t>Frontend: Análisis y definición de las acciones permitidas en la pantalla de taller, Generación de los inserts a la tabla de actionsections y actions, implementación de los 24 permisos en la pantalla de taller</t>
+  </si>
+  <si>
+    <t>recalculo del total de la nota en cada modificacion de la misma</t>
+  </si>
+  <si>
+    <t>Permiso de visualizacion de costos, validacion del precio minimo en el metal agranel de costo * gramos *1.30 y en productos</t>
+  </si>
+  <si>
+    <t>Reunion para mostrar Avances y tomar ajustes</t>
+  </si>
+  <si>
+    <t>Rediseño de filtros en la consulta de taller, estatus de taller, técnico del taller</t>
   </si>
 </sst>
 </file>
@@ -1484,6 +1532,33 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1499,38 +1574,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1866,7 +1914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K364"/>
+  <dimension ref="A1:K380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8097,9 +8145,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="5"/>
-      <c r="C321" s="61">
+      <c r="C321" s="9">
         <v>46078</v>
       </c>
       <c r="D321" s="13" t="s">
@@ -8115,341 +8163,501 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="5"/>
-      <c r="C322" s="61"/>
-      <c r="D322" s="13"/>
-      <c r="E322" s="2"/>
-      <c r="F322" s="2"/>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C322" s="9">
+        <v>46079</v>
+      </c>
+      <c r="D322" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E322" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="F322" s="2">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="H322" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A323" s="5"/>
-      <c r="C323" s="61"/>
-      <c r="D323" s="13"/>
-      <c r="E323" s="2"/>
-      <c r="F323" s="2"/>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C323" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D323" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="E323" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F323" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H323" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A324" s="5"/>
-      <c r="E324" s="2"/>
-      <c r="F324" s="2"/>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A325" s="83" t="s">
+      <c r="C324" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D324" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="E324" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="F324" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H324" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A325" s="5"/>
+      <c r="C325" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D325" s="71" t="s">
+        <v>332</v>
+      </c>
+      <c r="E325" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F325" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H325" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A326" s="5"/>
+      <c r="C326" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D326" s="71" t="s">
+        <v>335</v>
+      </c>
+      <c r="E326" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F326" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H326" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A327" s="5"/>
+      <c r="C327" s="9">
+        <v>46080</v>
+      </c>
+      <c r="D327" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E327" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F327" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="H327" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A328" s="5"/>
+      <c r="C328" s="9">
+        <v>46081</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="E328" s="2">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="F328" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="H328" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A329" s="5"/>
+      <c r="C329" s="9">
+        <v>46081</v>
+      </c>
+      <c r="D329" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E329" s="2">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F329" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="H329" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A330" s="5"/>
+      <c r="C330" s="9">
+        <v>46081</v>
+      </c>
+      <c r="D330" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="E330" s="2">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="F330" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="H330" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A331" s="5"/>
+      <c r="C331" s="9">
+        <v>46081</v>
+      </c>
+      <c r="D331" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="E331" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="F331" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H331" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A332" s="5"/>
+      <c r="C332" s="9"/>
+      <c r="D332" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E332" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F332" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H332" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A333" s="5"/>
+      <c r="C333" s="9">
+        <v>46081</v>
+      </c>
+      <c r="D333" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E333" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F333" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H333" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A334" s="5"/>
+      <c r="C334" s="61">
+        <v>46090</v>
+      </c>
+      <c r="D334" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="E334" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F334" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="H334" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A335" s="5"/>
+      <c r="C335" s="61">
+        <v>46090</v>
+      </c>
+      <c r="D335" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="E335" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="F335" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H335" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A336" s="5"/>
+      <c r="C336" s="61">
+        <v>46090</v>
+      </c>
+      <c r="D336" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="E336" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F336" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H336" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A337" s="5"/>
+      <c r="C337" s="61">
+        <v>46090</v>
+      </c>
+      <c r="D337" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E337" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F337" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H337" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A338" s="5"/>
+      <c r="C338" s="61"/>
+      <c r="D338" s="13"/>
+      <c r="E338" s="2"/>
+      <c r="F338" s="2"/>
+    </row>
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A339" s="5"/>
+      <c r="C339" s="61"/>
+      <c r="D339" s="13"/>
+      <c r="E339" s="2"/>
+      <c r="F339" s="2"/>
+    </row>
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A340" s="5"/>
+      <c r="E340" s="2"/>
+      <c r="F340" s="2"/>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A341" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B325" s="83"/>
-      <c r="C325" s="83"/>
-      <c r="D325" s="83"/>
-      <c r="E325" s="83"/>
-      <c r="F325" s="83"/>
-      <c r="G325" s="16">
-        <f>SUM(G2:G324)</f>
+      <c r="B341" s="75"/>
+      <c r="C341" s="75"/>
+      <c r="D341" s="75"/>
+      <c r="E341" s="75"/>
+      <c r="F341" s="75"/>
+      <c r="G341" s="16">
+        <f>SUM(G2:G340)</f>
         <v>314.78999999999996</v>
       </c>
-      <c r="H325" s="16">
-        <f>SUM(H2:H324)</f>
-        <v>160.30000000000001</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A326" s="83" t="s">
+      <c r="H341" s="16">
+        <f>SUM(H2:H340)</f>
+        <v>181.8</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A342" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="B326" s="83"/>
-      <c r="C326" s="83"/>
-      <c r="D326" s="83"/>
-      <c r="E326" s="83"/>
-      <c r="F326" s="83"/>
-      <c r="G326" s="16">
+      <c r="B342" s="75"/>
+      <c r="C342" s="75"/>
+      <c r="D342" s="75"/>
+      <c r="E342" s="75"/>
+      <c r="F342" s="75"/>
+      <c r="G342" s="16">
         <v>200</v>
       </c>
-      <c r="H326" s="16">
+      <c r="H342" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A327" s="83" t="s">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A343" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B327" s="83"/>
-      <c r="C327" s="83"/>
-      <c r="D327" s="83"/>
-      <c r="E327" s="83"/>
-      <c r="F327" s="83"/>
-      <c r="G327" s="17">
-        <f>G326*G325</f>
+      <c r="B343" s="75"/>
+      <c r="C343" s="75"/>
+      <c r="D343" s="75"/>
+      <c r="E343" s="75"/>
+      <c r="F343" s="75"/>
+      <c r="G343" s="17">
+        <f>G342*G341</f>
         <v>62957.999999999993</v>
       </c>
-      <c r="H327" s="18">
-        <f>H326*H325</f>
-        <v>48090</v>
-      </c>
-      <c r="J327">
+      <c r="H343" s="18">
+        <f>H342*H341</f>
+        <v>54540</v>
+      </c>
+      <c r="J343">
         <v>-500</v>
       </c>
     </row>
-    <row r="328" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A328" s="83" t="s">
+    <row r="344" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A344" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="B328" s="83"/>
-      <c r="C328" s="83"/>
-      <c r="D328" s="83"/>
-      <c r="E328" s="83"/>
-      <c r="F328" s="83"/>
-      <c r="G328" s="71">
-        <f>G327+H327</f>
-        <v>111048</v>
-      </c>
-      <c r="H328" s="71"/>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A329" s="10"/>
-      <c r="B329" s="74" t="s">
+      <c r="B344" s="75"/>
+      <c r="C344" s="75"/>
+      <c r="D344" s="75"/>
+      <c r="E344" s="75"/>
+      <c r="F344" s="75"/>
+      <c r="G344" s="80">
+        <f>G343+H343</f>
+        <v>117498</v>
+      </c>
+      <c r="H344" s="80"/>
+    </row>
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A345" s="10"/>
+      <c r="B345" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="C329" s="74"/>
-      <c r="D329" s="74"/>
-      <c r="E329" s="74"/>
-      <c r="F329" s="74"/>
-      <c r="G329" s="21"/>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A330" s="11">
+      <c r="C345" s="83"/>
+      <c r="D345" s="83"/>
+      <c r="E345" s="83"/>
+      <c r="F345" s="83"/>
+      <c r="G345" s="21"/>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A346" s="11">
         <v>45109</v>
       </c>
-      <c r="B330" s="75" t="s">
+      <c r="B346" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="C330" s="75"/>
-      <c r="D330" s="75"/>
-      <c r="E330" s="75"/>
-      <c r="F330" s="75"/>
-      <c r="G330" s="77">
+      <c r="C346" s="84"/>
+      <c r="D346" s="84"/>
+      <c r="E346" s="84"/>
+      <c r="F346" s="84"/>
+      <c r="G346" s="85">
         <v>10000</v>
       </c>
-      <c r="H330" s="77"/>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A331" s="11"/>
-      <c r="B331" s="79" t="s">
+      <c r="H346" s="85"/>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A347" s="11"/>
+      <c r="B347" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="C331" s="79"/>
-      <c r="D331" s="79"/>
-      <c r="E331" s="79"/>
-      <c r="F331" s="79"/>
-      <c r="G331" s="77">
+      <c r="C347" s="86"/>
+      <c r="D347" s="86"/>
+      <c r="E347" s="86"/>
+      <c r="F347" s="86"/>
+      <c r="G347" s="85">
         <v>5000</v>
       </c>
-      <c r="H331" s="77"/>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A332" s="11">
+      <c r="H347" s="85"/>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A348" s="11">
         <v>45278</v>
       </c>
-      <c r="B332" s="76" t="s">
+      <c r="B348" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="C332" s="76"/>
-      <c r="D332" s="76"/>
-      <c r="E332" s="76"/>
-      <c r="F332" s="76"/>
-      <c r="G332" s="77">
+      <c r="C348" s="76"/>
+      <c r="D348" s="76"/>
+      <c r="E348" s="76"/>
+      <c r="F348" s="76"/>
+      <c r="G348" s="85">
         <v>9800</v>
       </c>
-      <c r="H332" s="77"/>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A333" s="11"/>
-      <c r="B333" s="76"/>
-      <c r="C333" s="76"/>
-      <c r="D333" s="76"/>
-      <c r="E333" s="76"/>
-      <c r="F333" s="76"/>
-      <c r="G333" s="78"/>
-      <c r="H333" s="78"/>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A334" s="11"/>
-      <c r="B334" s="76"/>
-      <c r="C334" s="76"/>
-      <c r="D334" s="76"/>
-      <c r="E334" s="76"/>
-      <c r="F334" s="76"/>
-      <c r="G334" s="78"/>
-      <c r="H334" s="78"/>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A335" s="11"/>
-      <c r="B335" s="76"/>
-      <c r="C335" s="76"/>
-      <c r="D335" s="76"/>
-      <c r="E335" s="76"/>
-      <c r="F335" s="76"/>
-      <c r="G335" s="78"/>
-      <c r="H335" s="78"/>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A336" s="11"/>
-      <c r="B336" s="76" t="s">
+      <c r="H348" s="85"/>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A349" s="11"/>
+      <c r="B349" s="76"/>
+      <c r="C349" s="76"/>
+      <c r="D349" s="76"/>
+      <c r="E349" s="76"/>
+      <c r="F349" s="76"/>
+      <c r="G349" s="85">
+        <v>78298</v>
+      </c>
+      <c r="H349" s="85"/>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" s="11"/>
+      <c r="B350" s="76"/>
+      <c r="C350" s="76"/>
+      <c r="D350" s="76"/>
+      <c r="E350" s="76"/>
+      <c r="F350" s="76"/>
+      <c r="G350" s="85"/>
+      <c r="H350" s="85"/>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A351" s="11"/>
+      <c r="B351" s="76"/>
+      <c r="C351" s="76"/>
+      <c r="D351" s="76"/>
+      <c r="E351" s="76"/>
+      <c r="F351" s="76"/>
+      <c r="G351" s="85"/>
+      <c r="H351" s="85"/>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A352" s="11"/>
+      <c r="B352" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C336" s="76"/>
-      <c r="D336" s="76"/>
-      <c r="E336" s="76"/>
-      <c r="F336" s="76"/>
-      <c r="G336" s="77">
-        <f>SUM(G330:H335)</f>
-        <v>24800</v>
-      </c>
-      <c r="H336" s="77"/>
-    </row>
-    <row r="337" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A337" s="72" t="s">
+      <c r="C352" s="76"/>
+      <c r="D352" s="76"/>
+      <c r="E352" s="76"/>
+      <c r="F352" s="76"/>
+      <c r="G352" s="85">
+        <f>SUM(G346:H351)</f>
+        <v>103098</v>
+      </c>
+      <c r="H352" s="85"/>
+    </row>
+    <row r="353" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A353" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="B337" s="72"/>
-      <c r="C337" s="72"/>
-      <c r="D337" s="72"/>
-      <c r="E337" s="72"/>
-      <c r="F337" s="72"/>
-      <c r="G337" s="73">
-        <f>G328-G336</f>
-        <v>86248</v>
-      </c>
-      <c r="H337" s="73"/>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A338" s="11"/>
-      <c r="B338" s="12"/>
-      <c r="C338" s="12"/>
-      <c r="D338" s="12"/>
-      <c r="E338" s="12"/>
-      <c r="F338" s="12"/>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A339" s="11"/>
-      <c r="B339" s="12"/>
-      <c r="C339" s="12"/>
-      <c r="D339" s="12"/>
-      <c r="E339" s="12"/>
-      <c r="F339" s="12"/>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A340" s="11"/>
-      <c r="B340" s="12"/>
-      <c r="C340" s="12"/>
-      <c r="D340" s="12"/>
-      <c r="E340" s="12"/>
-      <c r="F340" s="12"/>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A341" s="11"/>
-      <c r="B341" s="12"/>
-      <c r="C341" s="12"/>
-      <c r="D341" s="12"/>
-      <c r="E341" s="12"/>
-      <c r="F341" s="12"/>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A342" s="11"/>
-      <c r="B342" s="12"/>
-      <c r="C342" s="12"/>
-      <c r="D342" s="12"/>
-      <c r="E342" s="12"/>
-      <c r="F342" s="12"/>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A343" s="11"/>
-      <c r="B343" s="12"/>
-      <c r="C343" s="12"/>
-      <c r="D343" s="12"/>
-      <c r="E343" s="12"/>
-      <c r="F343" s="12"/>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A344" s="11"/>
-      <c r="B344" s="12"/>
-      <c r="C344" s="12"/>
-      <c r="D344" s="12"/>
-      <c r="E344" s="12"/>
-      <c r="F344" s="12"/>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A345" s="11"/>
-      <c r="B345" s="12"/>
-      <c r="C345" s="12"/>
-      <c r="D345" s="12"/>
-      <c r="E345" s="12"/>
-      <c r="F345" s="12"/>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A346" s="11"/>
-      <c r="B346" s="12"/>
-      <c r="C346" s="12"/>
-      <c r="D346" s="12"/>
-      <c r="E346" s="12"/>
-      <c r="F346" s="12"/>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A347" s="11"/>
-      <c r="B347" s="12"/>
-      <c r="C347" s="12"/>
-      <c r="D347" s="12"/>
-      <c r="E347" s="12"/>
-      <c r="F347" s="12"/>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A348" s="11"/>
-      <c r="B348" s="12"/>
-      <c r="C348" s="12"/>
-      <c r="D348" s="12"/>
-      <c r="E348" s="12"/>
-      <c r="F348" s="12"/>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A349" s="11"/>
-      <c r="B349" s="12"/>
-      <c r="C349" s="12"/>
-      <c r="D349" s="12"/>
-      <c r="E349" s="12"/>
-      <c r="F349" s="12"/>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A350" s="11"/>
-      <c r="B350" s="12"/>
-      <c r="C350" s="12"/>
-      <c r="D350" s="12"/>
-      <c r="E350" s="12"/>
-      <c r="F350" s="12"/>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A351" s="11"/>
-      <c r="B351" s="12"/>
-      <c r="C351" s="12"/>
-      <c r="D351" s="12"/>
-      <c r="E351" s="12"/>
-      <c r="F351" s="12"/>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A352" s="11"/>
-      <c r="B352" s="12"/>
-      <c r="C352" s="12"/>
-      <c r="D352" s="12"/>
-      <c r="E352" s="12"/>
-      <c r="F352" s="12"/>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A353" s="11"/>
-      <c r="B353" s="12"/>
-      <c r="C353" s="12"/>
-      <c r="D353" s="12"/>
-      <c r="E353" s="12"/>
-      <c r="F353" s="12"/>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B353" s="81"/>
+      <c r="C353" s="81"/>
+      <c r="D353" s="81"/>
+      <c r="E353" s="81"/>
+      <c r="F353" s="81"/>
+      <c r="G353" s="82">
+        <f>G344-G352</f>
+        <v>14400</v>
+      </c>
+      <c r="H353" s="82"/>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
       <c r="B354" s="12"/>
       <c r="C354" s="12"/>
@@ -8457,7 +8665,7 @@
       <c r="E354" s="12"/>
       <c r="F354" s="12"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="11"/>
       <c r="B355" s="12"/>
       <c r="C355" s="12"/>
@@ -8465,191 +8673,319 @@
       <c r="E355" s="12"/>
       <c r="F355" s="12"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A356" s="9"/>
-      <c r="B356" s="84" t="s">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="11"/>
+      <c r="B356" s="12"/>
+      <c r="C356" s="12"/>
+      <c r="D356" s="12"/>
+      <c r="E356" s="12"/>
+      <c r="F356" s="12"/>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A357" s="11"/>
+      <c r="B357" s="12"/>
+      <c r="C357" s="12"/>
+      <c r="D357" s="12"/>
+      <c r="E357" s="12"/>
+      <c r="F357" s="12"/>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A358" s="11"/>
+      <c r="B358" s="12"/>
+      <c r="C358" s="12"/>
+      <c r="D358" s="12"/>
+      <c r="E358" s="12"/>
+      <c r="F358" s="12"/>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A359" s="11"/>
+      <c r="B359" s="12"/>
+      <c r="C359" s="12"/>
+      <c r="D359" s="12"/>
+      <c r="E359" s="12"/>
+      <c r="F359" s="12"/>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="11"/>
+      <c r="B360" s="12"/>
+      <c r="C360" s="12"/>
+      <c r="D360" s="12"/>
+      <c r="E360" s="12"/>
+      <c r="F360" s="12"/>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A361" s="11"/>
+      <c r="B361" s="12"/>
+      <c r="C361" s="12"/>
+      <c r="D361" s="12"/>
+      <c r="E361" s="12"/>
+      <c r="F361" s="12"/>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A362" s="11"/>
+      <c r="B362" s="12"/>
+      <c r="C362" s="12"/>
+      <c r="D362" s="12"/>
+      <c r="E362" s="12"/>
+      <c r="F362" s="12"/>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A363" s="11"/>
+      <c r="B363" s="12"/>
+      <c r="C363" s="12"/>
+      <c r="D363" s="12"/>
+      <c r="E363" s="12"/>
+      <c r="F363" s="12"/>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A364" s="11"/>
+      <c r="B364" s="12"/>
+      <c r="C364" s="12"/>
+      <c r="D364" s="12"/>
+      <c r="E364" s="12"/>
+      <c r="F364" s="12"/>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A365" s="11"/>
+      <c r="B365" s="12"/>
+      <c r="C365" s="12"/>
+      <c r="D365" s="12"/>
+      <c r="E365" s="12"/>
+      <c r="F365" s="12"/>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A366" s="11"/>
+      <c r="B366" s="12"/>
+      <c r="C366" s="12"/>
+      <c r="D366" s="12"/>
+      <c r="E366" s="12"/>
+      <c r="F366" s="12"/>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A367" s="11"/>
+      <c r="B367" s="12"/>
+      <c r="C367" s="12"/>
+      <c r="D367" s="12"/>
+      <c r="E367" s="12"/>
+      <c r="F367" s="12"/>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A368" s="11"/>
+      <c r="B368" s="12"/>
+      <c r="C368" s="12"/>
+      <c r="D368" s="12"/>
+      <c r="E368" s="12"/>
+      <c r="F368" s="12"/>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A369" s="11"/>
+      <c r="B369" s="12"/>
+      <c r="C369" s="12"/>
+      <c r="D369" s="12"/>
+      <c r="E369" s="12"/>
+      <c r="F369" s="12"/>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A370" s="11"/>
+      <c r="B370" s="12"/>
+      <c r="C370" s="12"/>
+      <c r="D370" s="12"/>
+      <c r="E370" s="12"/>
+      <c r="F370" s="12"/>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A371" s="11"/>
+      <c r="B371" s="12"/>
+      <c r="C371" s="12"/>
+      <c r="D371" s="12"/>
+      <c r="E371" s="12"/>
+      <c r="F371" s="12"/>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A372" s="9"/>
+      <c r="B372" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="C356" s="84"/>
-      <c r="D356" s="84"/>
-      <c r="E356" s="84"/>
-      <c r="F356" s="84"/>
-      <c r="G356" s="20"/>
-      <c r="H356" s="20"/>
-      <c r="I356" s="7">
-        <f>G325+H325</f>
-        <v>475.09</v>
-      </c>
-      <c r="J356" s="7">
-        <f>I356</f>
-        <v>475.09</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A357" s="5"/>
-      <c r="B357" s="85" t="s">
+      <c r="C372" s="77"/>
+      <c r="D372" s="77"/>
+      <c r="E372" s="77"/>
+      <c r="F372" s="77"/>
+      <c r="G372" s="20"/>
+      <c r="H372" s="20"/>
+      <c r="I372" s="7">
+        <f>G341+H341</f>
+        <v>496.59</v>
+      </c>
+      <c r="J372" s="7">
+        <f>I372</f>
+        <v>496.59</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A373" s="5"/>
+      <c r="B373" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="C357" s="85"/>
-      <c r="D357" s="85"/>
-      <c r="E357" s="85"/>
-      <c r="F357" s="85"/>
-      <c r="I357" s="7">
+      <c r="C373" s="78"/>
+      <c r="D373" s="78"/>
+      <c r="E373" s="78"/>
+      <c r="F373" s="78"/>
+      <c r="I373" s="7">
         <v>300</v>
       </c>
-      <c r="J357" s="7">
+      <c r="J373" s="7">
         <v>200</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A358" s="5"/>
-      <c r="B358" s="85" t="s">
+    <row r="374" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A374" s="5"/>
+      <c r="B374" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="C358" s="85"/>
-      <c r="D358" s="85"/>
-      <c r="E358" s="85"/>
-      <c r="F358" s="85"/>
-      <c r="I358" s="8">
-        <f>I357*I356</f>
-        <v>142527</v>
-      </c>
-      <c r="J358" s="8">
-        <f>J357*J356</f>
-        <v>95018</v>
-      </c>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A359" s="22"/>
-      <c r="B359" s="86" t="s">
+      <c r="C374" s="78"/>
+      <c r="D374" s="78"/>
+      <c r="E374" s="78"/>
+      <c r="F374" s="78"/>
+      <c r="I374" s="8">
+        <f>I373*I372</f>
+        <v>148977</v>
+      </c>
+      <c r="J374" s="8">
+        <f>J373*J372</f>
+        <v>99318</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A375" s="22"/>
+      <c r="B375" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="C359" s="86"/>
-      <c r="D359" s="86"/>
-      <c r="E359" s="86"/>
-      <c r="F359" s="86"/>
-      <c r="G359" s="23"/>
-      <c r="H359" s="23"/>
-      <c r="I359" s="24"/>
-      <c r="J359" s="24"/>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A360" s="25">
+      <c r="C375" s="79"/>
+      <c r="D375" s="79"/>
+      <c r="E375" s="79"/>
+      <c r="F375" s="79"/>
+      <c r="G375" s="23"/>
+      <c r="H375" s="23"/>
+      <c r="I375" s="24"/>
+      <c r="J375" s="24"/>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A376" s="25">
         <v>45109</v>
       </c>
-      <c r="B360" s="81" t="s">
+      <c r="B376" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="C360" s="81"/>
-      <c r="D360" s="81"/>
-      <c r="E360" s="81"/>
-      <c r="F360" s="81"/>
-      <c r="G360" s="26"/>
-      <c r="H360" s="26"/>
-      <c r="I360" s="27">
+      <c r="C376" s="73"/>
+      <c r="D376" s="73"/>
+      <c r="E376" s="73"/>
+      <c r="F376" s="73"/>
+      <c r="G376" s="26"/>
+      <c r="H376" s="26"/>
+      <c r="I376" s="27">
         <v>10000</v>
       </c>
-      <c r="J360" s="27">
+      <c r="J376" s="27">
         <v>10000</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A361" s="25"/>
-      <c r="B361" s="28"/>
-      <c r="C361" s="28"/>
-      <c r="D361" s="28"/>
-      <c r="E361" s="28"/>
-      <c r="F361" s="28"/>
-      <c r="G361" s="26"/>
-      <c r="H361" s="26"/>
-      <c r="I361" s="29"/>
-      <c r="J361" s="29"/>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A362" s="25"/>
-      <c r="B362" s="28"/>
-      <c r="C362" s="28"/>
-      <c r="D362" s="28"/>
-      <c r="E362" s="28"/>
-      <c r="F362" s="28"/>
-      <c r="G362" s="26"/>
-      <c r="H362" s="26"/>
-      <c r="I362" s="29"/>
-      <c r="J362" s="29"/>
-    </row>
-    <row r="363" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A363" s="25"/>
-      <c r="B363" s="82" t="s">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A377" s="25"/>
+      <c r="B377" s="28"/>
+      <c r="C377" s="28"/>
+      <c r="D377" s="28"/>
+      <c r="E377" s="28"/>
+      <c r="F377" s="28"/>
+      <c r="G377" s="26"/>
+      <c r="H377" s="26"/>
+      <c r="I377" s="29"/>
+      <c r="J377" s="29"/>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A378" s="25"/>
+      <c r="B378" s="28"/>
+      <c r="C378" s="28"/>
+      <c r="D378" s="28"/>
+      <c r="E378" s="28"/>
+      <c r="F378" s="28"/>
+      <c r="G378" s="26"/>
+      <c r="H378" s="26"/>
+      <c r="I378" s="29"/>
+      <c r="J378" s="29"/>
+    </row>
+    <row r="379" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A379" s="25"/>
+      <c r="B379" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="C363" s="82"/>
-      <c r="D363" s="82"/>
-      <c r="E363" s="82"/>
-      <c r="F363" s="82"/>
-      <c r="G363" s="26"/>
-      <c r="H363" s="26"/>
-      <c r="I363" s="30">
-        <f>SUM(I360:I362)</f>
+      <c r="C379" s="74"/>
+      <c r="D379" s="74"/>
+      <c r="E379" s="74"/>
+      <c r="F379" s="74"/>
+      <c r="G379" s="26"/>
+      <c r="H379" s="26"/>
+      <c r="I379" s="30">
+        <f>SUM(I376:I378)</f>
         <v>10000</v>
       </c>
-      <c r="J363" s="30">
-        <f>SUM(J360:J362)</f>
+      <c r="J379" s="30">
+        <f>SUM(J376:J378)</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A364" s="31">
+    <row r="380" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A380" s="31">
         <v>45109</v>
       </c>
-      <c r="B364" s="80" t="s">
+      <c r="B380" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C364" s="80"/>
-      <c r="D364" s="80"/>
-      <c r="E364" s="80"/>
-      <c r="F364" s="80"/>
-      <c r="G364" s="32"/>
-      <c r="H364" s="32"/>
-      <c r="I364" s="33">
-        <f>I358-I363</f>
-        <v>132527</v>
-      </c>
-      <c r="J364" s="33">
-        <f>J358-J363</f>
-        <v>85018</v>
+      <c r="C380" s="72"/>
+      <c r="D380" s="72"/>
+      <c r="E380" s="72"/>
+      <c r="F380" s="72"/>
+      <c r="G380" s="32"/>
+      <c r="H380" s="32"/>
+      <c r="I380" s="33">
+        <f>I374-I379</f>
+        <v>138977</v>
+      </c>
+      <c r="J380" s="33">
+        <f>J374-J379</f>
+        <v>89318</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B364:F364"/>
-    <mergeCell ref="B360:F360"/>
-    <mergeCell ref="B363:F363"/>
-    <mergeCell ref="A326:F326"/>
-    <mergeCell ref="A325:F325"/>
-    <mergeCell ref="A327:F327"/>
-    <mergeCell ref="A328:F328"/>
-    <mergeCell ref="B334:F334"/>
-    <mergeCell ref="B335:F335"/>
-    <mergeCell ref="B356:F356"/>
-    <mergeCell ref="B357:F357"/>
-    <mergeCell ref="B358:F358"/>
-    <mergeCell ref="B359:F359"/>
-    <mergeCell ref="G328:H328"/>
-    <mergeCell ref="A337:F337"/>
-    <mergeCell ref="G337:H337"/>
-    <mergeCell ref="B329:F329"/>
-    <mergeCell ref="B330:F330"/>
-    <mergeCell ref="B336:F336"/>
-    <mergeCell ref="G330:H330"/>
-    <mergeCell ref="G331:H331"/>
-    <mergeCell ref="G336:H336"/>
-    <mergeCell ref="G333:H333"/>
-    <mergeCell ref="G334:H334"/>
-    <mergeCell ref="G335:H335"/>
-    <mergeCell ref="G332:H332"/>
-    <mergeCell ref="B332:F332"/>
-    <mergeCell ref="B331:F331"/>
-    <mergeCell ref="B333:F333"/>
+    <mergeCell ref="G344:H344"/>
+    <mergeCell ref="A353:F353"/>
+    <mergeCell ref="G353:H353"/>
+    <mergeCell ref="B345:F345"/>
+    <mergeCell ref="B346:F346"/>
+    <mergeCell ref="B352:F352"/>
+    <mergeCell ref="G346:H346"/>
+    <mergeCell ref="G347:H347"/>
+    <mergeCell ref="G352:H352"/>
+    <mergeCell ref="G349:H349"/>
+    <mergeCell ref="G350:H350"/>
+    <mergeCell ref="G351:H351"/>
+    <mergeCell ref="G348:H348"/>
+    <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B347:F347"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="B379:F379"/>
+    <mergeCell ref="A342:F342"/>
+    <mergeCell ref="A341:F341"/>
+    <mergeCell ref="A343:F343"/>
+    <mergeCell ref="A344:F344"/>
+    <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B372:F372"/>
+    <mergeCell ref="B373:F373"/>
+    <mergeCell ref="B374:F374"/>
+    <mergeCell ref="B375:F375"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -9460,7 +9796,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6078F90-1BFA-44D9-9906-5A72B5F0645C}">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -9937,173 +10273,288 @@
       </c>
       <c r="C57" s="88"/>
     </row>
-    <row r="58" spans="1:3" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="51"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="53"/>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="48"/>
+      <c r="B58" s="66" t="s">
+        <v>330</v>
+      </c>
+      <c r="C58" s="87">
+        <v>5250</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="43"/>
-      <c r="B59" s="43" t="s">
+      <c r="A59" s="48"/>
+      <c r="B59" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="C59" s="92"/>
+    </row>
+    <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="48"/>
+      <c r="B60" s="67" t="s">
+        <v>333</v>
+      </c>
+      <c r="C60" s="92"/>
+    </row>
+    <row r="61" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="48"/>
+      <c r="B61" s="67" t="s">
+        <v>334</v>
+      </c>
+      <c r="C61" s="92"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="48"/>
+      <c r="B62" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="C62" s="92"/>
+    </row>
+    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="48"/>
+      <c r="B63" s="67" t="s">
+        <v>335</v>
+      </c>
+      <c r="C63" s="92"/>
+    </row>
+    <row r="64" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="48"/>
+      <c r="B64" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="C64" s="92"/>
+    </row>
+    <row r="65" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="48"/>
+      <c r="B65" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C65" s="92"/>
+    </row>
+    <row r="66" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="48"/>
+      <c r="B66" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" s="92"/>
+    </row>
+    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="48"/>
+      <c r="B67" s="67" t="s">
+        <v>339</v>
+      </c>
+      <c r="C67" s="92"/>
+    </row>
+    <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="48"/>
+      <c r="B68" s="67" t="s">
+        <v>340</v>
+      </c>
+      <c r="C68" s="92"/>
+    </row>
+    <row r="69" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="48"/>
+      <c r="B69" s="67" t="s">
+        <v>341</v>
+      </c>
+      <c r="C69" s="92"/>
+    </row>
+    <row r="70" spans="1:3" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="48"/>
+      <c r="B70" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="C70" s="88"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="48"/>
+      <c r="B71" s="62"/>
+      <c r="C71" s="63"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="48"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="63"/>
+    </row>
+    <row r="73" spans="1:3" s="42" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="51"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="53"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="43"/>
+      <c r="B74" s="43" t="s">
         <v>247</v>
       </c>
-      <c r="C59" s="46">
-        <f>SUM(C2:C58)</f>
-        <v>32900</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
+      <c r="C74" s="46">
+        <f>SUM(C2:C73)</f>
+        <v>38150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="55">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="55">
         <v>45690</v>
       </c>
-      <c r="B61" s="48" t="s">
+      <c r="B76" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C61" s="54">
+      <c r="C76" s="54">
         <v>2300</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="55"/>
-      <c r="B62" s="48" t="s">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="55"/>
+      <c r="B77" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="C62" s="54">
+      <c r="C77" s="54">
         <v>2250</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="55">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="55">
         <v>45804</v>
       </c>
-      <c r="B63" s="48" t="s">
+      <c r="B78" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="C63" s="54">
+      <c r="C78" s="54">
         <v>2700</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="55">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="55">
         <v>45839</v>
       </c>
-      <c r="B64" s="48" t="s">
+      <c r="B79" s="48" t="s">
         <v>278</v>
       </c>
-      <c r="C64" s="54">
+      <c r="C79" s="54">
         <v>4200</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="55"/>
-      <c r="B65" s="48"/>
-      <c r="C65" s="54">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="55"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="54">
         <v>4500</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="55">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="55">
         <v>46266</v>
       </c>
-      <c r="B66" s="48" t="s">
+      <c r="B81" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="C66" s="54">
+      <c r="C81" s="54">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="55"/>
-      <c r="B67" s="48" t="s">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="55"/>
+      <c r="B82" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="C67" s="54">
+      <c r="C82" s="54">
         <v>2550</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="55">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="55">
         <v>46073</v>
       </c>
-      <c r="B68" s="48" t="s">
+      <c r="B83" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="54">
+      <c r="C83" s="54">
         <v>4800</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="55"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="54"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="54"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="43"/>
-      <c r="B71" s="43" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="55">
+        <v>46089</v>
+      </c>
+      <c r="B84" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C84" s="54">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="55"/>
+      <c r="B85" s="48"/>
+      <c r="C85" s="54"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="54"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="43"/>
+      <c r="B87" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="C71" s="46">
-        <f>SUM(C60:C70)</f>
-        <v>25400</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6" t="s">
+      <c r="C87" s="46">
+        <f>SUM(C75:C86)</f>
+        <v>31400</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C72" s="47">
-        <f>C59-C71</f>
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="B76" s="13" t="s">
+      <c r="C88" s="47">
+        <f>C74-C87</f>
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="B92" s="13" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="13" t="s">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="13" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="B78" s="13" t="s">
+    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="B94" s="13" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B79" s="13" t="s">
+    <row r="95" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B95" s="13" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B80" s="13" t="s">
+    <row r="96" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B96" s="13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="81" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B81" s="13" t="s">
+    <row r="97" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B97" s="13" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="82" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B82" s="13" t="s">
+    <row r="98" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B98" s="13" t="s">
         <v>317</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="C58:C70"/>
     <mergeCell ref="C46:C57"/>
     <mergeCell ref="C39:C45"/>
     <mergeCell ref="C2:C4"/>

--- a/Documents/Actividades realizadas/ActividadesN__.xlsx
+++ b/Documents/Actividades realizadas/ActividadesN__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\1.- VioletaSystem\Documents\Actividades realizadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DDC944-032F-48EC-ADE9-ABD6600F64C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C411D5-6F1B-4FF3-AE0A-5B186204C330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="349">
   <si>
     <t>Descripción</t>
   </si>
@@ -1078,6 +1078,12 @@
   </si>
   <si>
     <t>Rediseño de filtros en la consulta de taller, estatus de taller, técnico del taller</t>
+  </si>
+  <si>
+    <t>Aprobación masiva en todos los tipos de estatus que tiene el taller desde la lista de talleres</t>
+  </si>
+  <si>
+    <t>Solución de problemas con la comilla simple en el código de barras</t>
   </si>
 </sst>
 </file>
@@ -1535,30 +1541,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1574,11 +1556,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1914,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K380"/>
+  <dimension ref="A1:K382"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8449,229 +8455,249 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A338" s="5"/>
-      <c r="C338" s="61"/>
-      <c r="D338" s="13"/>
-      <c r="E338" s="2"/>
-      <c r="F338" s="2"/>
+      <c r="C338" s="61">
+        <v>46103</v>
+      </c>
+      <c r="D338" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="E338" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="F338" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H338" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="5"/>
-      <c r="C339" s="61"/>
-      <c r="D339" s="13"/>
-      <c r="E339" s="2"/>
-      <c r="F339" s="2"/>
+      <c r="C339" s="61">
+        <v>46103</v>
+      </c>
+      <c r="D339" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E339" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F339" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H339" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="5"/>
+      <c r="C340" s="61"/>
+      <c r="D340" s="13"/>
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A341" s="75" t="s">
+      <c r="A341" s="5"/>
+      <c r="C341" s="61"/>
+      <c r="D341" s="13"/>
+      <c r="E341" s="2"/>
+      <c r="F341" s="2"/>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A342" s="5"/>
+      <c r="E342" s="2"/>
+      <c r="F342" s="2"/>
+    </row>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A343" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B341" s="75"/>
-      <c r="C341" s="75"/>
-      <c r="D341" s="75"/>
-      <c r="E341" s="75"/>
-      <c r="F341" s="75"/>
-      <c r="G341" s="16">
-        <f>SUM(G2:G340)</f>
+      <c r="B343" s="83"/>
+      <c r="C343" s="83"/>
+      <c r="D343" s="83"/>
+      <c r="E343" s="83"/>
+      <c r="F343" s="83"/>
+      <c r="G343" s="16">
+        <f>SUM(G2:G342)</f>
         <v>314.78999999999996</v>
       </c>
-      <c r="H341" s="16">
-        <f>SUM(H2:H340)</f>
-        <v>181.8</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A342" s="75" t="s">
+      <c r="H343" s="16">
+        <f>SUM(H2:H342)</f>
+        <v>186.8</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A344" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B342" s="75"/>
-      <c r="C342" s="75"/>
-      <c r="D342" s="75"/>
-      <c r="E342" s="75"/>
-      <c r="F342" s="75"/>
-      <c r="G342" s="16">
+      <c r="B344" s="83"/>
+      <c r="C344" s="83"/>
+      <c r="D344" s="83"/>
+      <c r="E344" s="83"/>
+      <c r="F344" s="83"/>
+      <c r="G344" s="16">
         <v>200</v>
       </c>
-      <c r="H342" s="16">
+      <c r="H344" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A343" s="75" t="s">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A345" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="B343" s="75"/>
-      <c r="C343" s="75"/>
-      <c r="D343" s="75"/>
-      <c r="E343" s="75"/>
-      <c r="F343" s="75"/>
-      <c r="G343" s="17">
-        <f>G342*G341</f>
-        <v>62957.999999999993</v>
-      </c>
-      <c r="H343" s="18">
-        <f>H342*H341</f>
-        <v>54540</v>
-      </c>
-      <c r="J343">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="344" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A344" s="75" t="s">
-        <v>58</v>
-      </c>
-      <c r="B344" s="75"/>
-      <c r="C344" s="75"/>
-      <c r="D344" s="75"/>
-      <c r="E344" s="75"/>
-      <c r="F344" s="75"/>
-      <c r="G344" s="80">
-        <f>G343+H343</f>
-        <v>117498</v>
-      </c>
-      <c r="H344" s="80"/>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A345" s="10"/>
-      <c r="B345" s="83" t="s">
-        <v>60</v>
-      </c>
+      <c r="B345" s="83"/>
       <c r="C345" s="83"/>
       <c r="D345" s="83"/>
       <c r="E345" s="83"/>
       <c r="F345" s="83"/>
-      <c r="G345" s="21"/>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A346" s="11">
-        <v>45109</v>
-      </c>
-      <c r="B346" s="84" t="s">
-        <v>59</v>
-      </c>
-      <c r="C346" s="84"/>
-      <c r="D346" s="84"/>
-      <c r="E346" s="84"/>
-      <c r="F346" s="84"/>
-      <c r="G346" s="85">
-        <v>10000</v>
-      </c>
-      <c r="H346" s="85"/>
+      <c r="G345" s="17">
+        <f>G344*G343</f>
+        <v>62957.999999999993</v>
+      </c>
+      <c r="H345" s="18">
+        <f>H344*H343</f>
+        <v>56040</v>
+      </c>
+      <c r="J345">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A346" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B346" s="83"/>
+      <c r="C346" s="83"/>
+      <c r="D346" s="83"/>
+      <c r="E346" s="83"/>
+      <c r="F346" s="83"/>
+      <c r="G346" s="72">
+        <f>G345+H345</f>
+        <v>118998</v>
+      </c>
+      <c r="H346" s="72"/>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A347" s="11"/>
-      <c r="B347" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C347" s="86"/>
-      <c r="D347" s="86"/>
-      <c r="E347" s="86"/>
-      <c r="F347" s="86"/>
-      <c r="G347" s="85">
-        <v>5000</v>
-      </c>
-      <c r="H347" s="85"/>
+      <c r="A347" s="10"/>
+      <c r="B347" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="C347" s="75"/>
+      <c r="D347" s="75"/>
+      <c r="E347" s="75"/>
+      <c r="F347" s="75"/>
+      <c r="G347" s="21"/>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="11">
-        <v>45278</v>
+        <v>45109</v>
       </c>
       <c r="B348" s="76" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C348" s="76"/>
       <c r="D348" s="76"/>
       <c r="E348" s="76"/>
       <c r="F348" s="76"/>
-      <c r="G348" s="85">
-        <v>9800</v>
-      </c>
-      <c r="H348" s="85"/>
+      <c r="G348" s="78">
+        <v>10000</v>
+      </c>
+      <c r="H348" s="78"/>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" s="11"/>
-      <c r="B349" s="76"/>
-      <c r="C349" s="76"/>
-      <c r="D349" s="76"/>
-      <c r="E349" s="76"/>
-      <c r="F349" s="76"/>
-      <c r="G349" s="85">
-        <v>78298</v>
-      </c>
-      <c r="H349" s="85"/>
+      <c r="B349" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="C349" s="79"/>
+      <c r="D349" s="79"/>
+      <c r="E349" s="79"/>
+      <c r="F349" s="79"/>
+      <c r="G349" s="78">
+        <v>5000</v>
+      </c>
+      <c r="H349" s="78"/>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A350" s="11"/>
-      <c r="B350" s="76"/>
-      <c r="C350" s="76"/>
-      <c r="D350" s="76"/>
-      <c r="E350" s="76"/>
-      <c r="F350" s="76"/>
-      <c r="G350" s="85"/>
-      <c r="H350" s="85"/>
+      <c r="A350" s="11">
+        <v>45278</v>
+      </c>
+      <c r="B350" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C350" s="77"/>
+      <c r="D350" s="77"/>
+      <c r="E350" s="77"/>
+      <c r="F350" s="77"/>
+      <c r="G350" s="78">
+        <v>9800</v>
+      </c>
+      <c r="H350" s="78"/>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="11"/>
-      <c r="B351" s="76"/>
-      <c r="C351" s="76"/>
-      <c r="D351" s="76"/>
-      <c r="E351" s="76"/>
-      <c r="F351" s="76"/>
-      <c r="G351" s="85"/>
-      <c r="H351" s="85"/>
+      <c r="B351" s="77"/>
+      <c r="C351" s="77"/>
+      <c r="D351" s="77"/>
+      <c r="E351" s="77"/>
+      <c r="F351" s="77"/>
+      <c r="G351" s="78">
+        <v>78298</v>
+      </c>
+      <c r="H351" s="78"/>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="11"/>
-      <c r="B352" s="76" t="s">
-        <v>62</v>
-      </c>
-      <c r="C352" s="76"/>
-      <c r="D352" s="76"/>
-      <c r="E352" s="76"/>
-      <c r="F352" s="76"/>
-      <c r="G352" s="85">
-        <f>SUM(G346:H351)</f>
-        <v>103098</v>
-      </c>
-      <c r="H352" s="85"/>
-    </row>
-    <row r="353" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A353" s="81" t="s">
-        <v>61</v>
-      </c>
-      <c r="B353" s="81"/>
-      <c r="C353" s="81"/>
-      <c r="D353" s="81"/>
-      <c r="E353" s="81"/>
-      <c r="F353" s="81"/>
-      <c r="G353" s="82">
-        <f>G344-G352</f>
-        <v>14400</v>
-      </c>
-      <c r="H353" s="82"/>
+      <c r="B352" s="77"/>
+      <c r="C352" s="77"/>
+      <c r="D352" s="77"/>
+      <c r="E352" s="77"/>
+      <c r="F352" s="77"/>
+      <c r="G352" s="78"/>
+      <c r="H352" s="78"/>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="11"/>
+      <c r="B353" s="77"/>
+      <c r="C353" s="77"/>
+      <c r="D353" s="77"/>
+      <c r="E353" s="77"/>
+      <c r="F353" s="77"/>
+      <c r="G353" s="78"/>
+      <c r="H353" s="78"/>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
-      <c r="B354" s="12"/>
-      <c r="C354" s="12"/>
-      <c r="D354" s="12"/>
-      <c r="E354" s="12"/>
-      <c r="F354" s="12"/>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A355" s="11"/>
-      <c r="B355" s="12"/>
-      <c r="C355" s="12"/>
-      <c r="D355" s="12"/>
-      <c r="E355" s="12"/>
-      <c r="F355" s="12"/>
+      <c r="B354" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C354" s="77"/>
+      <c r="D354" s="77"/>
+      <c r="E354" s="77"/>
+      <c r="F354" s="77"/>
+      <c r="G354" s="78">
+        <f>SUM(G348:H353)</f>
+        <v>103098</v>
+      </c>
+      <c r="H354" s="78"/>
+    </row>
+    <row r="355" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A355" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B355" s="73"/>
+      <c r="C355" s="73"/>
+      <c r="D355" s="73"/>
+      <c r="E355" s="73"/>
+      <c r="F355" s="73"/>
+      <c r="G355" s="74">
+        <f>G346-G354</f>
+        <v>15900</v>
+      </c>
+      <c r="H355" s="74"/>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="11"/>
@@ -8802,190 +8828,206 @@
       <c r="F371" s="12"/>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A372" s="9"/>
-      <c r="B372" s="77" t="s">
+      <c r="A372" s="11"/>
+      <c r="B372" s="12"/>
+      <c r="C372" s="12"/>
+      <c r="D372" s="12"/>
+      <c r="E372" s="12"/>
+      <c r="F372" s="12"/>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A373" s="11"/>
+      <c r="B373" s="12"/>
+      <c r="C373" s="12"/>
+      <c r="D373" s="12"/>
+      <c r="E373" s="12"/>
+      <c r="F373" s="12"/>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A374" s="9"/>
+      <c r="B374" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="C372" s="77"/>
-      <c r="D372" s="77"/>
-      <c r="E372" s="77"/>
-      <c r="F372" s="77"/>
-      <c r="G372" s="20"/>
-      <c r="H372" s="20"/>
-      <c r="I372" s="7">
-        <f>G341+H341</f>
-        <v>496.59</v>
-      </c>
-      <c r="J372" s="7">
-        <f>I372</f>
-        <v>496.59</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A373" s="5"/>
-      <c r="B373" s="78" t="s">
+      <c r="C374" s="84"/>
+      <c r="D374" s="84"/>
+      <c r="E374" s="84"/>
+      <c r="F374" s="84"/>
+      <c r="G374" s="20"/>
+      <c r="H374" s="20"/>
+      <c r="I374" s="7">
+        <f>G343+H343</f>
+        <v>501.59</v>
+      </c>
+      <c r="J374" s="7">
+        <f>I374</f>
+        <v>501.59</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A375" s="5"/>
+      <c r="B375" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="C373" s="78"/>
-      <c r="D373" s="78"/>
-      <c r="E373" s="78"/>
-      <c r="F373" s="78"/>
-      <c r="I373" s="7">
+      <c r="C375" s="85"/>
+      <c r="D375" s="85"/>
+      <c r="E375" s="85"/>
+      <c r="F375" s="85"/>
+      <c r="I375" s="7">
         <v>300</v>
       </c>
-      <c r="J373" s="7">
+      <c r="J375" s="7">
         <v>200</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A374" s="5"/>
-      <c r="B374" s="78" t="s">
+    <row r="376" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A376" s="5"/>
+      <c r="B376" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="C374" s="78"/>
-      <c r="D374" s="78"/>
-      <c r="E374" s="78"/>
-      <c r="F374" s="78"/>
-      <c r="I374" s="8">
-        <f>I373*I372</f>
-        <v>148977</v>
-      </c>
-      <c r="J374" s="8">
-        <f>J373*J372</f>
-        <v>99318</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A375" s="22"/>
-      <c r="B375" s="79" t="s">
+      <c r="C376" s="85"/>
+      <c r="D376" s="85"/>
+      <c r="E376" s="85"/>
+      <c r="F376" s="85"/>
+      <c r="I376" s="8">
+        <f>I375*I374</f>
+        <v>150477</v>
+      </c>
+      <c r="J376" s="8">
+        <f>J375*J374</f>
+        <v>100318</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A377" s="22"/>
+      <c r="B377" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="C375" s="79"/>
-      <c r="D375" s="79"/>
-      <c r="E375" s="79"/>
-      <c r="F375" s="79"/>
-      <c r="G375" s="23"/>
-      <c r="H375" s="23"/>
-      <c r="I375" s="24"/>
-      <c r="J375" s="24"/>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A376" s="25">
+      <c r="C377" s="86"/>
+      <c r="D377" s="86"/>
+      <c r="E377" s="86"/>
+      <c r="F377" s="86"/>
+      <c r="G377" s="23"/>
+      <c r="H377" s="23"/>
+      <c r="I377" s="24"/>
+      <c r="J377" s="24"/>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A378" s="25">
         <v>45109</v>
       </c>
-      <c r="B376" s="73" t="s">
+      <c r="B378" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C376" s="73"/>
-      <c r="D376" s="73"/>
-      <c r="E376" s="73"/>
-      <c r="F376" s="73"/>
-      <c r="G376" s="26"/>
-      <c r="H376" s="26"/>
-      <c r="I376" s="27">
-        <v>10000</v>
-      </c>
-      <c r="J376" s="27">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A377" s="25"/>
-      <c r="B377" s="28"/>
-      <c r="C377" s="28"/>
-      <c r="D377" s="28"/>
-      <c r="E377" s="28"/>
-      <c r="F377" s="28"/>
-      <c r="G377" s="26"/>
-      <c r="H377" s="26"/>
-      <c r="I377" s="29"/>
-      <c r="J377" s="29"/>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A378" s="25"/>
-      <c r="B378" s="28"/>
-      <c r="C378" s="28"/>
-      <c r="D378" s="28"/>
-      <c r="E378" s="28"/>
-      <c r="F378" s="28"/>
+      <c r="C378" s="81"/>
+      <c r="D378" s="81"/>
+      <c r="E378" s="81"/>
+      <c r="F378" s="81"/>
       <c r="G378" s="26"/>
       <c r="H378" s="26"/>
-      <c r="I378" s="29"/>
-      <c r="J378" s="29"/>
-    </row>
-    <row r="379" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="I378" s="27">
+        <v>10000</v>
+      </c>
+      <c r="J378" s="27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" s="25"/>
-      <c r="B379" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="C379" s="74"/>
-      <c r="D379" s="74"/>
-      <c r="E379" s="74"/>
-      <c r="F379" s="74"/>
+      <c r="B379" s="28"/>
+      <c r="C379" s="28"/>
+      <c r="D379" s="28"/>
+      <c r="E379" s="28"/>
+      <c r="F379" s="28"/>
       <c r="G379" s="26"/>
       <c r="H379" s="26"/>
-      <c r="I379" s="30">
-        <f>SUM(I376:I378)</f>
+      <c r="I379" s="29"/>
+      <c r="J379" s="29"/>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A380" s="25"/>
+      <c r="B380" s="28"/>
+      <c r="C380" s="28"/>
+      <c r="D380" s="28"/>
+      <c r="E380" s="28"/>
+      <c r="F380" s="28"/>
+      <c r="G380" s="26"/>
+      <c r="H380" s="26"/>
+      <c r="I380" s="29"/>
+      <c r="J380" s="29"/>
+    </row>
+    <row r="381" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A381" s="25"/>
+      <c r="B381" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="C381" s="82"/>
+      <c r="D381" s="82"/>
+      <c r="E381" s="82"/>
+      <c r="F381" s="82"/>
+      <c r="G381" s="26"/>
+      <c r="H381" s="26"/>
+      <c r="I381" s="30">
+        <f>SUM(I378:I380)</f>
         <v>10000</v>
       </c>
-      <c r="J379" s="30">
-        <f>SUM(J376:J378)</f>
+      <c r="J381" s="30">
+        <f>SUM(J378:J380)</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A380" s="31">
+    <row r="382" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A382" s="31">
         <v>45109</v>
       </c>
-      <c r="B380" s="72" t="s">
+      <c r="B382" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C380" s="72"/>
-      <c r="D380" s="72"/>
-      <c r="E380" s="72"/>
-      <c r="F380" s="72"/>
-      <c r="G380" s="32"/>
-      <c r="H380" s="32"/>
-      <c r="I380" s="33">
-        <f>I374-I379</f>
-        <v>138977</v>
-      </c>
-      <c r="J380" s="33">
-        <f>J374-J379</f>
-        <v>89318</v>
+      <c r="C382" s="80"/>
+      <c r="D382" s="80"/>
+      <c r="E382" s="80"/>
+      <c r="F382" s="80"/>
+      <c r="G382" s="32"/>
+      <c r="H382" s="32"/>
+      <c r="I382" s="33">
+        <f>I376-I381</f>
+        <v>140477</v>
+      </c>
+      <c r="J382" s="33">
+        <f>J376-J381</f>
+        <v>90318</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="G344:H344"/>
-    <mergeCell ref="A353:F353"/>
-    <mergeCell ref="G353:H353"/>
-    <mergeCell ref="B345:F345"/>
-    <mergeCell ref="B346:F346"/>
+    <mergeCell ref="B382:F382"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="B381:F381"/>
+    <mergeCell ref="A344:F344"/>
+    <mergeCell ref="A343:F343"/>
+    <mergeCell ref="A345:F345"/>
+    <mergeCell ref="A346:F346"/>
     <mergeCell ref="B352:F352"/>
-    <mergeCell ref="G346:H346"/>
-    <mergeCell ref="G347:H347"/>
-    <mergeCell ref="G352:H352"/>
-    <mergeCell ref="G349:H349"/>
-    <mergeCell ref="G350:H350"/>
-    <mergeCell ref="G351:H351"/>
-    <mergeCell ref="G348:H348"/>
-    <mergeCell ref="B348:F348"/>
-    <mergeCell ref="B347:F347"/>
-    <mergeCell ref="B349:F349"/>
-    <mergeCell ref="B380:F380"/>
-    <mergeCell ref="B376:F376"/>
-    <mergeCell ref="B379:F379"/>
-    <mergeCell ref="A342:F342"/>
-    <mergeCell ref="A341:F341"/>
-    <mergeCell ref="A343:F343"/>
-    <mergeCell ref="A344:F344"/>
-    <mergeCell ref="B350:F350"/>
-    <mergeCell ref="B351:F351"/>
-    <mergeCell ref="B372:F372"/>
-    <mergeCell ref="B373:F373"/>
+    <mergeCell ref="B353:F353"/>
     <mergeCell ref="B374:F374"/>
     <mergeCell ref="B375:F375"/>
+    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="B377:F377"/>
+    <mergeCell ref="G346:H346"/>
+    <mergeCell ref="A355:F355"/>
+    <mergeCell ref="G355:H355"/>
+    <mergeCell ref="B347:F347"/>
+    <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="G348:H348"/>
+    <mergeCell ref="G349:H349"/>
+    <mergeCell ref="G354:H354"/>
+    <mergeCell ref="G351:H351"/>
+    <mergeCell ref="G352:H352"/>
+    <mergeCell ref="G353:H353"/>
+    <mergeCell ref="G350:H350"/>
+    <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="B351:F351"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Documents/Actividades realizadas/ActividadesN__.xlsx
+++ b/Documents/Actividades realizadas/ActividadesN__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\1.- VioletaSystem\Documents\Actividades realizadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C411D5-6F1B-4FF3-AE0A-5B186204C330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DD725C-42DF-4F8F-91F2-D189CC638D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="351">
   <si>
     <t>Descripción</t>
   </si>
@@ -1084,6 +1084,12 @@
   </si>
   <si>
     <t>Solución de problemas con la comilla simple en el código de barras</t>
+  </si>
+  <si>
+    <t>Funcionalidad de devolución del cliente</t>
+  </si>
+  <si>
+    <t>funcionalidad de regrear a cualquier estatus el taller</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K382"/>
+  <dimension ref="A1:K383"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8493,44 +8499,55 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="5"/>
-      <c r="C340" s="61"/>
-      <c r="D340" s="13"/>
-      <c r="E340" s="2"/>
-      <c r="F340" s="2"/>
+      <c r="C340" s="61">
+        <v>46103</v>
+      </c>
+      <c r="D340" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E340" s="2">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F340" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H340" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="5"/>
-      <c r="C341" s="61"/>
-      <c r="D341" s="13"/>
-      <c r="E341" s="2"/>
-      <c r="F341" s="2"/>
+      <c r="C341" s="61">
+        <v>46103</v>
+      </c>
+      <c r="D341" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="E341" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F341" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H341" s="14">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="5"/>
+      <c r="C342" s="61"/>
+      <c r="D342" s="13"/>
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A343" s="83" t="s">
-        <v>83</v>
-      </c>
-      <c r="B343" s="83"/>
-      <c r="C343" s="83"/>
-      <c r="D343" s="83"/>
-      <c r="E343" s="83"/>
-      <c r="F343" s="83"/>
-      <c r="G343" s="16">
-        <f>SUM(G2:G342)</f>
-        <v>314.78999999999996</v>
-      </c>
-      <c r="H343" s="16">
-        <f>SUM(H2:H342)</f>
-        <v>186.8</v>
-      </c>
+      <c r="A343" s="5"/>
+      <c r="E343" s="2"/>
+      <c r="F343" s="2"/>
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="83" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B344" s="83"/>
       <c r="C344" s="83"/>
@@ -8538,114 +8555,120 @@
       <c r="E344" s="83"/>
       <c r="F344" s="83"/>
       <c r="G344" s="16">
-        <v>200</v>
+        <f>SUM(G2:G343)</f>
+        <v>314.78999999999996</v>
       </c>
       <c r="H344" s="16">
-        <v>300</v>
+        <f>SUM(H2:H343)</f>
+        <v>190.3</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="83" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B345" s="83"/>
       <c r="C345" s="83"/>
       <c r="D345" s="83"/>
       <c r="E345" s="83"/>
       <c r="F345" s="83"/>
-      <c r="G345" s="17">
-        <f>G344*G343</f>
-        <v>62957.999999999993</v>
-      </c>
-      <c r="H345" s="18">
-        <f>H344*H343</f>
-        <v>56040</v>
-      </c>
-      <c r="J345">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="G345" s="16">
+        <v>200</v>
+      </c>
+      <c r="H345" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="83" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B346" s="83"/>
       <c r="C346" s="83"/>
       <c r="D346" s="83"/>
       <c r="E346" s="83"/>
       <c r="F346" s="83"/>
-      <c r="G346" s="72">
-        <f>G345+H345</f>
-        <v>118998</v>
-      </c>
-      <c r="H346" s="72"/>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A347" s="10"/>
-      <c r="B347" s="75" t="s">
+      <c r="G346" s="17">
+        <f>G345*G344</f>
+        <v>62957.999999999993</v>
+      </c>
+      <c r="H346" s="18">
+        <f>H345*H344</f>
+        <v>57090</v>
+      </c>
+      <c r="J346">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A347" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B347" s="83"/>
+      <c r="C347" s="83"/>
+      <c r="D347" s="83"/>
+      <c r="E347" s="83"/>
+      <c r="F347" s="83"/>
+      <c r="G347" s="72">
+        <f>G346+H346</f>
+        <v>120048</v>
+      </c>
+      <c r="H347" s="72"/>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A348" s="10"/>
+      <c r="B348" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="C347" s="75"/>
-      <c r="D347" s="75"/>
-      <c r="E347" s="75"/>
-      <c r="F347" s="75"/>
-      <c r="G347" s="21"/>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A348" s="11">
+      <c r="C348" s="75"/>
+      <c r="D348" s="75"/>
+      <c r="E348" s="75"/>
+      <c r="F348" s="75"/>
+      <c r="G348" s="21"/>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A349" s="11">
         <v>45109</v>
       </c>
-      <c r="B348" s="76" t="s">
+      <c r="B349" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="C348" s="76"/>
-      <c r="D348" s="76"/>
-      <c r="E348" s="76"/>
-      <c r="F348" s="76"/>
-      <c r="G348" s="78">
+      <c r="C349" s="76"/>
+      <c r="D349" s="76"/>
+      <c r="E349" s="76"/>
+      <c r="F349" s="76"/>
+      <c r="G349" s="78">
         <v>10000</v>
       </c>
-      <c r="H348" s="78"/>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A349" s="11"/>
-      <c r="B349" s="79" t="s">
+      <c r="H349" s="78"/>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" s="11"/>
+      <c r="B350" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="C349" s="79"/>
-      <c r="D349" s="79"/>
-      <c r="E349" s="79"/>
-      <c r="F349" s="79"/>
-      <c r="G349" s="78">
+      <c r="C350" s="79"/>
+      <c r="D350" s="79"/>
+      <c r="E350" s="79"/>
+      <c r="F350" s="79"/>
+      <c r="G350" s="78">
         <v>5000</v>
       </c>
-      <c r="H349" s="78"/>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A350" s="11">
+      <c r="H350" s="78"/>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A351" s="11">
         <v>45278</v>
       </c>
-      <c r="B350" s="77" t="s">
+      <c r="B351" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C350" s="77"/>
-      <c r="D350" s="77"/>
-      <c r="E350" s="77"/>
-      <c r="F350" s="77"/>
-      <c r="G350" s="78">
-        <v>9800</v>
-      </c>
-      <c r="H350" s="78"/>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A351" s="11"/>
-      <c r="B351" s="77"/>
       <c r="C351" s="77"/>
       <c r="D351" s="77"/>
       <c r="E351" s="77"/>
       <c r="F351" s="77"/>
       <c r="G351" s="78">
-        <v>78298</v>
+        <v>9800</v>
       </c>
       <c r="H351" s="78"/>
     </row>
@@ -8656,7 +8679,9 @@
       <c r="D352" s="77"/>
       <c r="E352" s="77"/>
       <c r="F352" s="77"/>
-      <c r="G352" s="78"/>
+      <c r="G352" s="78">
+        <v>78298</v>
+      </c>
       <c r="H352" s="78"/>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
@@ -8671,41 +8696,43 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
-      <c r="B354" s="77" t="s">
-        <v>62</v>
-      </c>
+      <c r="B354" s="77"/>
       <c r="C354" s="77"/>
       <c r="D354" s="77"/>
       <c r="E354" s="77"/>
       <c r="F354" s="77"/>
-      <c r="G354" s="78">
-        <f>SUM(G348:H353)</f>
+      <c r="G354" s="78"/>
+      <c r="H354" s="78"/>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A355" s="11"/>
+      <c r="B355" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C355" s="77"/>
+      <c r="D355" s="77"/>
+      <c r="E355" s="77"/>
+      <c r="F355" s="77"/>
+      <c r="G355" s="78">
+        <f>SUM(G349:H354)</f>
         <v>103098</v>
       </c>
-      <c r="H354" s="78"/>
-    </row>
-    <row r="355" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A355" s="73" t="s">
+      <c r="H355" s="78"/>
+    </row>
+    <row r="356" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A356" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B355" s="73"/>
-      <c r="C355" s="73"/>
-      <c r="D355" s="73"/>
-      <c r="E355" s="73"/>
-      <c r="F355" s="73"/>
-      <c r="G355" s="74">
-        <f>G346-G354</f>
-        <v>15900</v>
-      </c>
-      <c r="H355" s="74"/>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A356" s="11"/>
-      <c r="B356" s="12"/>
-      <c r="C356" s="12"/>
-      <c r="D356" s="12"/>
-      <c r="E356" s="12"/>
-      <c r="F356" s="12"/>
+      <c r="B356" s="73"/>
+      <c r="C356" s="73"/>
+      <c r="D356" s="73"/>
+      <c r="E356" s="73"/>
+      <c r="F356" s="73"/>
+      <c r="G356" s="74">
+        <f>G347-G355</f>
+        <v>16950</v>
+      </c>
+      <c r="H356" s="74"/>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="11"/>
@@ -8844,104 +8871,100 @@
       <c r="F373" s="12"/>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A374" s="9"/>
-      <c r="B374" s="84" t="s">
+      <c r="A374" s="11"/>
+      <c r="B374" s="12"/>
+      <c r="C374" s="12"/>
+      <c r="D374" s="12"/>
+      <c r="E374" s="12"/>
+      <c r="F374" s="12"/>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A375" s="9"/>
+      <c r="B375" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="C374" s="84"/>
-      <c r="D374" s="84"/>
-      <c r="E374" s="84"/>
-      <c r="F374" s="84"/>
-      <c r="G374" s="20"/>
-      <c r="H374" s="20"/>
-      <c r="I374" s="7">
-        <f>G343+H343</f>
-        <v>501.59</v>
-      </c>
-      <c r="J374" s="7">
-        <f>I374</f>
-        <v>501.59</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A375" s="5"/>
-      <c r="B375" s="85" t="s">
-        <v>57</v>
-      </c>
-      <c r="C375" s="85"/>
-      <c r="D375" s="85"/>
-      <c r="E375" s="85"/>
-      <c r="F375" s="85"/>
+      <c r="C375" s="84"/>
+      <c r="D375" s="84"/>
+      <c r="E375" s="84"/>
+      <c r="F375" s="84"/>
+      <c r="G375" s="20"/>
+      <c r="H375" s="20"/>
       <c r="I375" s="7">
-        <v>300</v>
+        <f>G344+H344</f>
+        <v>505.09</v>
       </c>
       <c r="J375" s="7">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+        <f>I375</f>
+        <v>505.09</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" s="5"/>
       <c r="B376" s="85" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C376" s="85"/>
       <c r="D376" s="85"/>
       <c r="E376" s="85"/>
       <c r="F376" s="85"/>
-      <c r="I376" s="8">
-        <f>I375*I374</f>
-        <v>150477</v>
-      </c>
-      <c r="J376" s="8">
-        <f>J375*J374</f>
-        <v>100318</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A377" s="22"/>
-      <c r="B377" s="86" t="s">
+      <c r="I376" s="7">
+        <v>300</v>
+      </c>
+      <c r="J376" s="7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A377" s="5"/>
+      <c r="B377" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="C377" s="85"/>
+      <c r="D377" s="85"/>
+      <c r="E377" s="85"/>
+      <c r="F377" s="85"/>
+      <c r="I377" s="8">
+        <f>I376*I375</f>
+        <v>151527</v>
+      </c>
+      <c r="J377" s="8">
+        <f>J376*J375</f>
+        <v>101018</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A378" s="22"/>
+      <c r="B378" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="C377" s="86"/>
-      <c r="D377" s="86"/>
-      <c r="E377" s="86"/>
-      <c r="F377" s="86"/>
-      <c r="G377" s="23"/>
-      <c r="H377" s="23"/>
-      <c r="I377" s="24"/>
-      <c r="J377" s="24"/>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A378" s="25">
+      <c r="C378" s="86"/>
+      <c r="D378" s="86"/>
+      <c r="E378" s="86"/>
+      <c r="F378" s="86"/>
+      <c r="G378" s="23"/>
+      <c r="H378" s="23"/>
+      <c r="I378" s="24"/>
+      <c r="J378" s="24"/>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A379" s="25">
         <v>45109</v>
       </c>
-      <c r="B378" s="81" t="s">
+      <c r="B379" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C378" s="81"/>
-      <c r="D378" s="81"/>
-      <c r="E378" s="81"/>
-      <c r="F378" s="81"/>
-      <c r="G378" s="26"/>
-      <c r="H378" s="26"/>
-      <c r="I378" s="27">
-        <v>10000</v>
-      </c>
-      <c r="J378" s="27">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A379" s="25"/>
-      <c r="B379" s="28"/>
-      <c r="C379" s="28"/>
-      <c r="D379" s="28"/>
-      <c r="E379" s="28"/>
-      <c r="F379" s="28"/>
+      <c r="C379" s="81"/>
+      <c r="D379" s="81"/>
+      <c r="E379" s="81"/>
+      <c r="F379" s="81"/>
       <c r="G379" s="26"/>
       <c r="H379" s="26"/>
-      <c r="I379" s="29"/>
-      <c r="J379" s="29"/>
+      <c r="I379" s="27">
+        <v>10000</v>
+      </c>
+      <c r="J379" s="27">
+        <v>10000</v>
+      </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" s="25"/>
@@ -8955,79 +8978,91 @@
       <c r="I380" s="29"/>
       <c r="J380" s="29"/>
     </row>
-    <row r="381" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" s="25"/>
-      <c r="B381" s="82" t="s">
-        <v>62</v>
-      </c>
-      <c r="C381" s="82"/>
-      <c r="D381" s="82"/>
-      <c r="E381" s="82"/>
-      <c r="F381" s="82"/>
+      <c r="B381" s="28"/>
+      <c r="C381" s="28"/>
+      <c r="D381" s="28"/>
+      <c r="E381" s="28"/>
+      <c r="F381" s="28"/>
       <c r="G381" s="26"/>
       <c r="H381" s="26"/>
-      <c r="I381" s="30">
-        <f>SUM(I378:I380)</f>
+      <c r="I381" s="29"/>
+      <c r="J381" s="29"/>
+    </row>
+    <row r="382" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A382" s="25"/>
+      <c r="B382" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="C382" s="82"/>
+      <c r="D382" s="82"/>
+      <c r="E382" s="82"/>
+      <c r="F382" s="82"/>
+      <c r="G382" s="26"/>
+      <c r="H382" s="26"/>
+      <c r="I382" s="30">
+        <f>SUM(I379:I381)</f>
         <v>10000</v>
       </c>
-      <c r="J381" s="30">
-        <f>SUM(J378:J380)</f>
+      <c r="J382" s="30">
+        <f>SUM(J379:J381)</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A382" s="31">
+    <row r="383" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A383" s="31">
         <v>45109</v>
       </c>
-      <c r="B382" s="80" t="s">
+      <c r="B383" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C382" s="80"/>
-      <c r="D382" s="80"/>
-      <c r="E382" s="80"/>
-      <c r="F382" s="80"/>
-      <c r="G382" s="32"/>
-      <c r="H382" s="32"/>
-      <c r="I382" s="33">
-        <f>I376-I381</f>
-        <v>140477</v>
-      </c>
-      <c r="J382" s="33">
-        <f>J376-J381</f>
-        <v>90318</v>
+      <c r="C383" s="80"/>
+      <c r="D383" s="80"/>
+      <c r="E383" s="80"/>
+      <c r="F383" s="80"/>
+      <c r="G383" s="32"/>
+      <c r="H383" s="32"/>
+      <c r="I383" s="33">
+        <f>I377-I382</f>
+        <v>141527</v>
+      </c>
+      <c r="J383" s="33">
+        <f>J377-J382</f>
+        <v>91018</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B383:F383"/>
+    <mergeCell ref="B379:F379"/>
     <mergeCell ref="B382:F382"/>
-    <mergeCell ref="B378:F378"/>
-    <mergeCell ref="B381:F381"/>
+    <mergeCell ref="A345:F345"/>
     <mergeCell ref="A344:F344"/>
-    <mergeCell ref="A343:F343"/>
-    <mergeCell ref="A345:F345"/>
     <mergeCell ref="A346:F346"/>
-    <mergeCell ref="B352:F352"/>
+    <mergeCell ref="A347:F347"/>
     <mergeCell ref="B353:F353"/>
-    <mergeCell ref="B374:F374"/>
+    <mergeCell ref="B354:F354"/>
     <mergeCell ref="B375:F375"/>
     <mergeCell ref="B376:F376"/>
     <mergeCell ref="B377:F377"/>
-    <mergeCell ref="G346:H346"/>
-    <mergeCell ref="A355:F355"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="G347:H347"/>
+    <mergeCell ref="A356:F356"/>
+    <mergeCell ref="G356:H356"/>
+    <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="B355:F355"/>
+    <mergeCell ref="G349:H349"/>
+    <mergeCell ref="G350:H350"/>
     <mergeCell ref="G355:H355"/>
-    <mergeCell ref="B347:F347"/>
-    <mergeCell ref="B348:F348"/>
-    <mergeCell ref="B354:F354"/>
-    <mergeCell ref="G348:H348"/>
-    <mergeCell ref="G349:H349"/>
+    <mergeCell ref="G352:H352"/>
+    <mergeCell ref="G353:H353"/>
     <mergeCell ref="G354:H354"/>
     <mergeCell ref="G351:H351"/>
-    <mergeCell ref="G352:H352"/>
-    <mergeCell ref="G353:H353"/>
-    <mergeCell ref="G350:H350"/>
+    <mergeCell ref="B351:F351"/>
     <mergeCell ref="B350:F350"/>
-    <mergeCell ref="B349:F349"/>
-    <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B352:F352"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/Documents/Actividades realizadas/ActividadesN__.xlsx
+++ b/Documents/Actividades realizadas/ActividadesN__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\1.- VioletaSystem\Documents\Actividades realizadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DD725C-42DF-4F8F-91F2-D189CC638D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05570031-43F5-41C0-9EE9-0C95EFAD6C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="355">
   <si>
     <t>Descripción</t>
   </si>
@@ -1090,6 +1090,18 @@
   </si>
   <si>
     <t>funcionalidad de regrear a cualquier estatus el taller</t>
+  </si>
+  <si>
+    <t>Lista de responsables de la devolución, alta, modificación, eliminación y edición</t>
+  </si>
+  <si>
+    <t>Instalación, configuración de taller para pruebas</t>
+  </si>
+  <si>
+    <t>Se agrega la lógica de generar folio de cotizacion al inicio en taller y que se pueda imprimir ticket, luego al convertirlo en un taller se genere folio de taller</t>
+  </si>
+  <si>
+    <t>Modificar el ticket para que muestre el metal del cliente y el metal que da la empresa</t>
   </si>
 </sst>
 </file>
@@ -1547,6 +1559,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1562,35 +1598,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1926,7 +1938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K383"/>
+  <dimension ref="A1:K387"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -7957,7 +7969,7 @@
       <c r="F309" s="2">
         <v>0.63888888888888884</v>
       </c>
-      <c r="H309" s="14">
+      <c r="H309" s="20">
         <v>5</v>
       </c>
     </row>
@@ -7973,7 +7985,7 @@
       <c r="F310" s="2">
         <v>0.56944444444444442</v>
       </c>
-      <c r="H310" s="14">
+      <c r="H310" s="20">
         <v>3</v>
       </c>
     </row>
@@ -7991,7 +8003,7 @@
       <c r="F311" s="2">
         <v>0.46527777777777779</v>
       </c>
-      <c r="H311" s="14">
+      <c r="H311" s="20">
         <v>3</v>
       </c>
     </row>
@@ -8009,7 +8021,7 @@
       <c r="F312" s="2">
         <v>0.55694444444444446</v>
       </c>
-      <c r="H312" s="14">
+      <c r="H312" s="20">
         <v>2</v>
       </c>
     </row>
@@ -8027,7 +8039,7 @@
       <c r="F313" s="2">
         <v>0.71875</v>
       </c>
-      <c r="H313" s="14">
+      <c r="H313" s="20">
         <v>3</v>
       </c>
     </row>
@@ -8045,7 +8057,7 @@
       <c r="F314" s="2">
         <v>0.83333333333333337</v>
       </c>
-      <c r="H314" s="14">
+      <c r="H314" s="20">
         <v>2</v>
       </c>
     </row>
@@ -8063,7 +8075,7 @@
       <c r="F315" s="2">
         <v>0.85416666666666663</v>
       </c>
-      <c r="H315" s="14">
+      <c r="H315" s="20">
         <v>0.5</v>
       </c>
     </row>
@@ -8081,7 +8093,7 @@
       <c r="F316" s="2">
         <v>0.875</v>
       </c>
-      <c r="H316" s="14">
+      <c r="H316" s="20">
         <v>0.5</v>
       </c>
     </row>
@@ -8099,7 +8111,7 @@
       <c r="F317" s="2">
         <v>0.8979166666666667</v>
       </c>
-      <c r="H317" s="14">
+      <c r="H317" s="20">
         <v>0.5</v>
       </c>
     </row>
@@ -8117,7 +8129,7 @@
       <c r="F318" s="2">
         <v>0.9555555555555556</v>
       </c>
-      <c r="H318" s="14">
+      <c r="H318" s="20">
         <v>1.5</v>
       </c>
     </row>
@@ -8135,7 +8147,7 @@
       <c r="F319" s="2">
         <v>0.46180555555555558</v>
       </c>
-      <c r="H319" s="14">
+      <c r="H319" s="20">
         <v>2</v>
       </c>
     </row>
@@ -8153,7 +8165,7 @@
       <c r="F320" s="2">
         <v>0.58680555555555558</v>
       </c>
-      <c r="H320" s="14">
+      <c r="H320" s="20">
         <v>2</v>
       </c>
     </row>
@@ -8171,7 +8183,7 @@
       <c r="F321" s="2">
         <v>0.3125</v>
       </c>
-      <c r="H321" s="14">
+      <c r="H321" s="20">
         <v>1.5</v>
       </c>
     </row>
@@ -8189,7 +8201,7 @@
       <c r="F322" s="2">
         <v>0.4861111111111111</v>
       </c>
-      <c r="H322" s="14">
+      <c r="H322" s="20">
         <v>1.5</v>
       </c>
     </row>
@@ -8207,7 +8219,7 @@
       <c r="F323" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H323" s="14">
+      <c r="H323" s="20">
         <v>2</v>
       </c>
     </row>
@@ -8225,7 +8237,7 @@
       <c r="F324" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H324" s="14">
+      <c r="H324" s="20">
         <v>0.5</v>
       </c>
     </row>
@@ -8243,7 +8255,7 @@
       <c r="F325" s="2">
         <v>0.5</v>
       </c>
-      <c r="H325" s="14">
+      <c r="H325" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8261,7 +8273,7 @@
       <c r="F326" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H326" s="14">
+      <c r="H326" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8279,7 +8291,7 @@
       <c r="F327" s="2">
         <v>0.625</v>
       </c>
-      <c r="H327" s="14">
+      <c r="H327" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8297,7 +8309,7 @@
       <c r="F328" s="2">
         <v>0.29166666666666669</v>
       </c>
-      <c r="H328" s="14">
+      <c r="H328" s="20">
         <v>2</v>
       </c>
     </row>
@@ -8315,7 +8327,7 @@
       <c r="F329" s="2">
         <v>0.35416666666666669</v>
       </c>
-      <c r="H329" s="14">
+      <c r="H329" s="20">
         <v>1.5</v>
       </c>
     </row>
@@ -8333,7 +8345,7 @@
       <c r="F330" s="2">
         <v>0.375</v>
       </c>
-      <c r="H330" s="14">
+      <c r="H330" s="20">
         <v>0.5</v>
       </c>
     </row>
@@ -8351,7 +8363,7 @@
       <c r="F331" s="2">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H331" s="14">
+      <c r="H331" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8367,7 +8379,7 @@
       <c r="F332" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H332" s="14">
+      <c r="H332" s="20">
         <v>1</v>
       </c>
     </row>
@@ -8385,13 +8397,13 @@
       <c r="F333" s="2">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H333" s="14">
+      <c r="H333" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="5"/>
-      <c r="C334" s="61">
+      <c r="C334" s="9">
         <v>46090</v>
       </c>
       <c r="D334" s="13" t="s">
@@ -8403,13 +8415,13 @@
       <c r="F334" s="2">
         <v>0.375</v>
       </c>
-      <c r="H334" s="14">
+      <c r="H334" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A335" s="5"/>
-      <c r="C335" s="61">
+      <c r="C335" s="9">
         <v>46090</v>
       </c>
       <c r="D335" s="13" t="s">
@@ -8421,13 +8433,13 @@
       <c r="F335" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H335" s="14">
+      <c r="H335" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="5"/>
-      <c r="C336" s="61">
+      <c r="C336" s="9">
         <v>46090</v>
       </c>
       <c r="D336" s="13" t="s">
@@ -8439,13 +8451,13 @@
       <c r="F336" s="2">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H336" s="14">
+      <c r="H336" s="20">
         <v>1.5</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="5"/>
-      <c r="C337" s="61">
+      <c r="C337" s="9">
         <v>46090</v>
       </c>
       <c r="D337" s="13" t="s">
@@ -8457,13 +8469,13 @@
       <c r="F337" s="2">
         <v>0.75</v>
       </c>
-      <c r="H337" s="14">
+      <c r="H337" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A338" s="5"/>
-      <c r="C338" s="61">
+      <c r="C338" s="9">
         <v>46103</v>
       </c>
       <c r="D338" s="13" t="s">
@@ -8475,13 +8487,13 @@
       <c r="F338" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H338" s="14">
+      <c r="H338" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="5"/>
-      <c r="C339" s="61">
+      <c r="C339" s="9">
         <v>46103</v>
       </c>
       <c r="D339" s="13" t="s">
@@ -8493,13 +8505,13 @@
       <c r="F339" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="H339" s="14">
+      <c r="H339" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="5"/>
-      <c r="C340" s="61">
+      <c r="C340" s="9">
         <v>46103</v>
       </c>
       <c r="D340" s="13" t="s">
@@ -8511,13 +8523,13 @@
       <c r="F340" s="2">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H340" s="14">
+      <c r="H340" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="5"/>
-      <c r="C341" s="61">
+      <c r="C341" s="9">
         <v>46103</v>
       </c>
       <c r="D341" s="13" t="s">
@@ -8529,242 +8541,282 @@
       <c r="F341" s="2">
         <v>0.72916666666666663</v>
       </c>
-      <c r="H341" s="14">
+      <c r="H341" s="20">
         <v>1.5</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A342" s="5"/>
-      <c r="C342" s="61"/>
-      <c r="D342" s="13"/>
-      <c r="E342" s="2"/>
-      <c r="F342" s="2"/>
+      <c r="C342" s="9">
+        <v>46103</v>
+      </c>
+      <c r="D342" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="E342" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F342" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="H342" s="20">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="5"/>
-      <c r="E343" s="2"/>
-      <c r="F343" s="2"/>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A344" s="83" t="s">
+      <c r="C343" s="9">
+        <v>46118</v>
+      </c>
+      <c r="D343" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E343" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F343" s="2">
+        <v>0.59375</v>
+      </c>
+      <c r="H343" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A344" s="5"/>
+      <c r="C344" s="61">
+        <v>46150</v>
+      </c>
+      <c r="D344" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E344" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="F344" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H344" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="345" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A345" s="5"/>
+      <c r="C345" s="61">
+        <v>46150</v>
+      </c>
+      <c r="D345" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="E345" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F345" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="H345" s="14">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A346" s="5"/>
+      <c r="C346" s="61"/>
+      <c r="D346" s="13"/>
+      <c r="E346" s="2"/>
+      <c r="F346" s="2"/>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A347" s="5"/>
+      <c r="E347" s="2"/>
+      <c r="F347" s="2"/>
+    </row>
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A348" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B344" s="83"/>
-      <c r="C344" s="83"/>
-      <c r="D344" s="83"/>
-      <c r="E344" s="83"/>
-      <c r="F344" s="83"/>
-      <c r="G344" s="16">
-        <f>SUM(G2:G343)</f>
-        <v>314.78999999999996</v>
-      </c>
-      <c r="H344" s="16">
-        <f>SUM(H2:H343)</f>
-        <v>190.3</v>
-      </c>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A345" s="83" t="s">
-        <v>57</v>
-      </c>
-      <c r="B345" s="83"/>
-      <c r="C345" s="83"/>
-      <c r="D345" s="83"/>
-      <c r="E345" s="83"/>
-      <c r="F345" s="83"/>
-      <c r="G345" s="16">
-        <v>200</v>
-      </c>
-      <c r="H345" s="16">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A346" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="B346" s="83"/>
-      <c r="C346" s="83"/>
-      <c r="D346" s="83"/>
-      <c r="E346" s="83"/>
-      <c r="F346" s="83"/>
-      <c r="G346" s="17">
-        <f>G345*G344</f>
-        <v>62957.999999999993</v>
-      </c>
-      <c r="H346" s="18">
-        <f>H345*H344</f>
-        <v>57090</v>
-      </c>
-      <c r="J346">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="347" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A347" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="B347" s="83"/>
-      <c r="C347" s="83"/>
-      <c r="D347" s="83"/>
-      <c r="E347" s="83"/>
-      <c r="F347" s="83"/>
-      <c r="G347" s="72">
-        <f>G346+H346</f>
-        <v>120048</v>
-      </c>
-      <c r="H347" s="72"/>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A348" s="10"/>
-      <c r="B348" s="75" t="s">
-        <v>60</v>
-      </c>
+      <c r="B348" s="75"/>
       <c r="C348" s="75"/>
       <c r="D348" s="75"/>
       <c r="E348" s="75"/>
       <c r="F348" s="75"/>
-      <c r="G348" s="21"/>
+      <c r="G348" s="16">
+        <f>SUM(G2:G347)</f>
+        <v>314.78999999999996</v>
+      </c>
+      <c r="H348" s="16">
+        <f>SUM(H2:H347)</f>
+        <v>198.3</v>
+      </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A349" s="11">
+      <c r="A349" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="B349" s="75"/>
+      <c r="C349" s="75"/>
+      <c r="D349" s="75"/>
+      <c r="E349" s="75"/>
+      <c r="F349" s="75"/>
+      <c r="G349" s="16">
+        <v>200</v>
+      </c>
+      <c r="H349" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="B350" s="75"/>
+      <c r="C350" s="75"/>
+      <c r="D350" s="75"/>
+      <c r="E350" s="75"/>
+      <c r="F350" s="75"/>
+      <c r="G350" s="17">
+        <f>G349*G348</f>
+        <v>62957.999999999993</v>
+      </c>
+      <c r="H350" s="18">
+        <f>H349*H348</f>
+        <v>59490</v>
+      </c>
+      <c r="J350">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A351" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="B351" s="75"/>
+      <c r="C351" s="75"/>
+      <c r="D351" s="75"/>
+      <c r="E351" s="75"/>
+      <c r="F351" s="75"/>
+      <c r="G351" s="80">
+        <f>G350+H350</f>
+        <v>122448</v>
+      </c>
+      <c r="H351" s="80"/>
+    </row>
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A352" s="10"/>
+      <c r="B352" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="C352" s="83"/>
+      <c r="D352" s="83"/>
+      <c r="E352" s="83"/>
+      <c r="F352" s="83"/>
+      <c r="G352" s="21"/>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A353" s="11">
         <v>45109</v>
       </c>
-      <c r="B349" s="76" t="s">
+      <c r="B353" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="C349" s="76"/>
-      <c r="D349" s="76"/>
-      <c r="E349" s="76"/>
-      <c r="F349" s="76"/>
-      <c r="G349" s="78">
+      <c r="C353" s="84"/>
+      <c r="D353" s="84"/>
+      <c r="E353" s="84"/>
+      <c r="F353" s="84"/>
+      <c r="G353" s="85">
         <v>10000</v>
       </c>
-      <c r="H349" s="78"/>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A350" s="11"/>
-      <c r="B350" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="C350" s="79"/>
-      <c r="D350" s="79"/>
-      <c r="E350" s="79"/>
-      <c r="F350" s="79"/>
-      <c r="G350" s="78">
-        <v>5000</v>
-      </c>
-      <c r="H350" s="78"/>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A351" s="11">
-        <v>45278</v>
-      </c>
-      <c r="B351" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="C351" s="77"/>
-      <c r="D351" s="77"/>
-      <c r="E351" s="77"/>
-      <c r="F351" s="77"/>
-      <c r="G351" s="78">
-        <v>9800</v>
-      </c>
-      <c r="H351" s="78"/>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A352" s="11"/>
-      <c r="B352" s="77"/>
-      <c r="C352" s="77"/>
-      <c r="D352" s="77"/>
-      <c r="E352" s="77"/>
-      <c r="F352" s="77"/>
-      <c r="G352" s="78">
-        <v>78298</v>
-      </c>
-      <c r="H352" s="78"/>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A353" s="11"/>
-      <c r="B353" s="77"/>
-      <c r="C353" s="77"/>
-      <c r="D353" s="77"/>
-      <c r="E353" s="77"/>
-      <c r="F353" s="77"/>
-      <c r="G353" s="78"/>
-      <c r="H353" s="78"/>
+      <c r="H353" s="85"/>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="11"/>
-      <c r="B354" s="77"/>
-      <c r="C354" s="77"/>
-      <c r="D354" s="77"/>
-      <c r="E354" s="77"/>
-      <c r="F354" s="77"/>
-      <c r="G354" s="78"/>
-      <c r="H354" s="78"/>
+      <c r="B354" s="86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C354" s="86"/>
+      <c r="D354" s="86"/>
+      <c r="E354" s="86"/>
+      <c r="F354" s="86"/>
+      <c r="G354" s="85">
+        <v>5000</v>
+      </c>
+      <c r="H354" s="85"/>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A355" s="11"/>
-      <c r="B355" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="C355" s="77"/>
-      <c r="D355" s="77"/>
-      <c r="E355" s="77"/>
-      <c r="F355" s="77"/>
-      <c r="G355" s="78">
-        <f>SUM(G349:H354)</f>
-        <v>103098</v>
-      </c>
-      <c r="H355" s="78"/>
-    </row>
-    <row r="356" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A356" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="B356" s="73"/>
-      <c r="C356" s="73"/>
-      <c r="D356" s="73"/>
-      <c r="E356" s="73"/>
-      <c r="F356" s="73"/>
-      <c r="G356" s="74">
-        <f>G347-G355</f>
-        <v>16950</v>
-      </c>
-      <c r="H356" s="74"/>
+      <c r="A355" s="11">
+        <v>45278</v>
+      </c>
+      <c r="B355" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C355" s="76"/>
+      <c r="D355" s="76"/>
+      <c r="E355" s="76"/>
+      <c r="F355" s="76"/>
+      <c r="G355" s="85">
+        <v>9800</v>
+      </c>
+      <c r="H355" s="85"/>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A356" s="11"/>
+      <c r="B356" s="76"/>
+      <c r="C356" s="76"/>
+      <c r="D356" s="76"/>
+      <c r="E356" s="76"/>
+      <c r="F356" s="76"/>
+      <c r="G356" s="85">
+        <v>78298</v>
+      </c>
+      <c r="H356" s="85"/>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="11"/>
-      <c r="B357" s="12"/>
-      <c r="C357" s="12"/>
-      <c r="D357" s="12"/>
-      <c r="E357" s="12"/>
-      <c r="F357" s="12"/>
+      <c r="B357" s="76"/>
+      <c r="C357" s="76"/>
+      <c r="D357" s="76"/>
+      <c r="E357" s="76"/>
+      <c r="F357" s="76"/>
+      <c r="G357" s="85"/>
+      <c r="H357" s="85"/>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="11"/>
-      <c r="B358" s="12"/>
-      <c r="C358" s="12"/>
-      <c r="D358" s="12"/>
-      <c r="E358" s="12"/>
-      <c r="F358" s="12"/>
+      <c r="B358" s="76"/>
+      <c r="C358" s="76"/>
+      <c r="D358" s="76"/>
+      <c r="E358" s="76"/>
+      <c r="F358" s="76"/>
+      <c r="G358" s="85"/>
+      <c r="H358" s="85"/>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="11"/>
-      <c r="B359" s="12"/>
-      <c r="C359" s="12"/>
-      <c r="D359" s="12"/>
-      <c r="E359" s="12"/>
-      <c r="F359" s="12"/>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A360" s="11"/>
-      <c r="B360" s="12"/>
-      <c r="C360" s="12"/>
-      <c r="D360" s="12"/>
-      <c r="E360" s="12"/>
-      <c r="F360" s="12"/>
+      <c r="B359" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="C359" s="76"/>
+      <c r="D359" s="76"/>
+      <c r="E359" s="76"/>
+      <c r="F359" s="76"/>
+      <c r="G359" s="85">
+        <f>SUM(G353:H358)</f>
+        <v>103098</v>
+      </c>
+      <c r="H359" s="85"/>
+    </row>
+    <row r="360" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A360" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="B360" s="81"/>
+      <c r="C360" s="81"/>
+      <c r="D360" s="81"/>
+      <c r="E360" s="81"/>
+      <c r="F360" s="81"/>
+      <c r="G360" s="82">
+        <f>G351-G359</f>
+        <v>19350</v>
+      </c>
+      <c r="H360" s="82"/>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="11"/>
@@ -8879,190 +8931,222 @@
       <c r="F374" s="12"/>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A375" s="9"/>
-      <c r="B375" s="84" t="s">
+      <c r="A375" s="11"/>
+      <c r="B375" s="12"/>
+      <c r="C375" s="12"/>
+      <c r="D375" s="12"/>
+      <c r="E375" s="12"/>
+      <c r="F375" s="12"/>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A376" s="11"/>
+      <c r="B376" s="12"/>
+      <c r="C376" s="12"/>
+      <c r="D376" s="12"/>
+      <c r="E376" s="12"/>
+      <c r="F376" s="12"/>
+    </row>
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A377" s="11"/>
+      <c r="B377" s="12"/>
+      <c r="C377" s="12"/>
+      <c r="D377" s="12"/>
+      <c r="E377" s="12"/>
+      <c r="F377" s="12"/>
+    </row>
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A378" s="11"/>
+      <c r="B378" s="12"/>
+      <c r="C378" s="12"/>
+      <c r="D378" s="12"/>
+      <c r="E378" s="12"/>
+      <c r="F378" s="12"/>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A379" s="9"/>
+      <c r="B379" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="C375" s="84"/>
-      <c r="D375" s="84"/>
-      <c r="E375" s="84"/>
-      <c r="F375" s="84"/>
-      <c r="G375" s="20"/>
-      <c r="H375" s="20"/>
-      <c r="I375" s="7">
-        <f>G344+H344</f>
-        <v>505.09</v>
-      </c>
-      <c r="J375" s="7">
-        <f>I375</f>
-        <v>505.09</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A376" s="5"/>
-      <c r="B376" s="85" t="s">
+      <c r="C379" s="77"/>
+      <c r="D379" s="77"/>
+      <c r="E379" s="77"/>
+      <c r="F379" s="77"/>
+      <c r="G379" s="20"/>
+      <c r="H379" s="20"/>
+      <c r="I379" s="7">
+        <f>G348+H348</f>
+        <v>513.08999999999992</v>
+      </c>
+      <c r="J379" s="7">
+        <f>I379</f>
+        <v>513.08999999999992</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A380" s="5"/>
+      <c r="B380" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="C376" s="85"/>
-      <c r="D376" s="85"/>
-      <c r="E376" s="85"/>
-      <c r="F376" s="85"/>
-      <c r="I376" s="7">
+      <c r="C380" s="78"/>
+      <c r="D380" s="78"/>
+      <c r="E380" s="78"/>
+      <c r="F380" s="78"/>
+      <c r="I380" s="7">
         <v>300</v>
       </c>
-      <c r="J376" s="7">
+      <c r="J380" s="7">
         <v>200</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A377" s="5"/>
-      <c r="B377" s="85" t="s">
+    <row r="381" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A381" s="5"/>
+      <c r="B381" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="C377" s="85"/>
-      <c r="D377" s="85"/>
-      <c r="E377" s="85"/>
-      <c r="F377" s="85"/>
-      <c r="I377" s="8">
-        <f>I376*I375</f>
-        <v>151527</v>
-      </c>
-      <c r="J377" s="8">
-        <f>J376*J375</f>
-        <v>101018</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A378" s="22"/>
-      <c r="B378" s="86" t="s">
+      <c r="C381" s="78"/>
+      <c r="D381" s="78"/>
+      <c r="E381" s="78"/>
+      <c r="F381" s="78"/>
+      <c r="I381" s="8">
+        <f>I380*I379</f>
+        <v>153926.99999999997</v>
+      </c>
+      <c r="J381" s="8">
+        <f>J380*J379</f>
+        <v>102617.99999999999</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A382" s="22"/>
+      <c r="B382" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="C378" s="86"/>
-      <c r="D378" s="86"/>
-      <c r="E378" s="86"/>
-      <c r="F378" s="86"/>
-      <c r="G378" s="23"/>
-      <c r="H378" s="23"/>
-      <c r="I378" s="24"/>
-      <c r="J378" s="24"/>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A379" s="25">
+      <c r="C382" s="79"/>
+      <c r="D382" s="79"/>
+      <c r="E382" s="79"/>
+      <c r="F382" s="79"/>
+      <c r="G382" s="23"/>
+      <c r="H382" s="23"/>
+      <c r="I382" s="24"/>
+      <c r="J382" s="24"/>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A383" s="25">
         <v>45109</v>
       </c>
-      <c r="B379" s="81" t="s">
+      <c r="B383" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="C379" s="81"/>
-      <c r="D379" s="81"/>
-      <c r="E379" s="81"/>
-      <c r="F379" s="81"/>
-      <c r="G379" s="26"/>
-      <c r="H379" s="26"/>
-      <c r="I379" s="27">
+      <c r="C383" s="73"/>
+      <c r="D383" s="73"/>
+      <c r="E383" s="73"/>
+      <c r="F383" s="73"/>
+      <c r="G383" s="26"/>
+      <c r="H383" s="26"/>
+      <c r="I383" s="27">
         <v>10000</v>
       </c>
-      <c r="J379" s="27">
+      <c r="J383" s="27">
         <v>10000</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A380" s="25"/>
-      <c r="B380" s="28"/>
-      <c r="C380" s="28"/>
-      <c r="D380" s="28"/>
-      <c r="E380" s="28"/>
-      <c r="F380" s="28"/>
-      <c r="G380" s="26"/>
-      <c r="H380" s="26"/>
-      <c r="I380" s="29"/>
-      <c r="J380" s="29"/>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A381" s="25"/>
-      <c r="B381" s="28"/>
-      <c r="C381" s="28"/>
-      <c r="D381" s="28"/>
-      <c r="E381" s="28"/>
-      <c r="F381" s="28"/>
-      <c r="G381" s="26"/>
-      <c r="H381" s="26"/>
-      <c r="I381" s="29"/>
-      <c r="J381" s="29"/>
-    </row>
-    <row r="382" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A382" s="25"/>
-      <c r="B382" s="82" t="s">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A384" s="25"/>
+      <c r="B384" s="28"/>
+      <c r="C384" s="28"/>
+      <c r="D384" s="28"/>
+      <c r="E384" s="28"/>
+      <c r="F384" s="28"/>
+      <c r="G384" s="26"/>
+      <c r="H384" s="26"/>
+      <c r="I384" s="29"/>
+      <c r="J384" s="29"/>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A385" s="25"/>
+      <c r="B385" s="28"/>
+      <c r="C385" s="28"/>
+      <c r="D385" s="28"/>
+      <c r="E385" s="28"/>
+      <c r="F385" s="28"/>
+      <c r="G385" s="26"/>
+      <c r="H385" s="26"/>
+      <c r="I385" s="29"/>
+      <c r="J385" s="29"/>
+    </row>
+    <row r="386" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A386" s="25"/>
+      <c r="B386" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="C382" s="82"/>
-      <c r="D382" s="82"/>
-      <c r="E382" s="82"/>
-      <c r="F382" s="82"/>
-      <c r="G382" s="26"/>
-      <c r="H382" s="26"/>
-      <c r="I382" s="30">
-        <f>SUM(I379:I381)</f>
+      <c r="C386" s="74"/>
+      <c r="D386" s="74"/>
+      <c r="E386" s="74"/>
+      <c r="F386" s="74"/>
+      <c r="G386" s="26"/>
+      <c r="H386" s="26"/>
+      <c r="I386" s="30">
+        <f>SUM(I383:I385)</f>
         <v>10000</v>
       </c>
-      <c r="J382" s="30">
-        <f>SUM(J379:J381)</f>
+      <c r="J386" s="30">
+        <f>SUM(J383:J385)</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A383" s="31">
+    <row r="387" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A387" s="31">
         <v>45109</v>
       </c>
-      <c r="B383" s="80" t="s">
+      <c r="B387" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C383" s="80"/>
-      <c r="D383" s="80"/>
-      <c r="E383" s="80"/>
-      <c r="F383" s="80"/>
-      <c r="G383" s="32"/>
-      <c r="H383" s="32"/>
-      <c r="I383" s="33">
-        <f>I377-I382</f>
-        <v>141527</v>
-      </c>
-      <c r="J383" s="33">
-        <f>J377-J382</f>
-        <v>91018</v>
+      <c r="C387" s="72"/>
+      <c r="D387" s="72"/>
+      <c r="E387" s="72"/>
+      <c r="F387" s="72"/>
+      <c r="G387" s="32"/>
+      <c r="H387" s="32"/>
+      <c r="I387" s="33">
+        <f>I381-I386</f>
+        <v>143926.99999999997</v>
+      </c>
+      <c r="J387" s="33">
+        <f>J381-J386</f>
+        <v>92617.999999999985</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B383:F383"/>
-    <mergeCell ref="B379:F379"/>
-    <mergeCell ref="B382:F382"/>
-    <mergeCell ref="A345:F345"/>
-    <mergeCell ref="A344:F344"/>
-    <mergeCell ref="A346:F346"/>
-    <mergeCell ref="A347:F347"/>
+    <mergeCell ref="G351:H351"/>
+    <mergeCell ref="A360:F360"/>
+    <mergeCell ref="G360:H360"/>
+    <mergeCell ref="B352:F352"/>
     <mergeCell ref="B353:F353"/>
-    <mergeCell ref="B354:F354"/>
-    <mergeCell ref="B375:F375"/>
-    <mergeCell ref="B376:F376"/>
-    <mergeCell ref="B377:F377"/>
-    <mergeCell ref="B378:F378"/>
-    <mergeCell ref="G347:H347"/>
-    <mergeCell ref="A356:F356"/>
-    <mergeCell ref="G356:H356"/>
-    <mergeCell ref="B348:F348"/>
-    <mergeCell ref="B349:F349"/>
-    <mergeCell ref="B355:F355"/>
-    <mergeCell ref="G349:H349"/>
-    <mergeCell ref="G350:H350"/>
-    <mergeCell ref="G355:H355"/>
-    <mergeCell ref="G352:H352"/>
+    <mergeCell ref="B359:F359"/>
     <mergeCell ref="G353:H353"/>
     <mergeCell ref="G354:H354"/>
-    <mergeCell ref="G351:H351"/>
-    <mergeCell ref="B351:F351"/>
-    <mergeCell ref="B350:F350"/>
-    <mergeCell ref="B352:F352"/>
+    <mergeCell ref="G359:H359"/>
+    <mergeCell ref="G356:H356"/>
+    <mergeCell ref="G357:H357"/>
+    <mergeCell ref="G358:H358"/>
+    <mergeCell ref="G355:H355"/>
+    <mergeCell ref="B355:F355"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B356:F356"/>
+    <mergeCell ref="B387:F387"/>
+    <mergeCell ref="B383:F383"/>
+    <mergeCell ref="B386:F386"/>
+    <mergeCell ref="A349:F349"/>
+    <mergeCell ref="A348:F348"/>
+    <mergeCell ref="A350:F350"/>
+    <mergeCell ref="A351:F351"/>
+    <mergeCell ref="B357:F357"/>
+    <mergeCell ref="B358:F358"/>
+    <mergeCell ref="B379:F379"/>
+    <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B381:F381"/>
+    <mergeCell ref="B382:F382"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -9071,7 +9155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B2F9DB-D849-4B99-B5E6-70BB7408BE44}">
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -9771,84 +9855,99 @@
       <c r="C79" s="54"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="48"/>
+      <c r="A80" s="55"/>
       <c r="B80" s="48"/>
       <c r="C80" s="54"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="43"/>
-      <c r="B81" s="43" t="s">
+      <c r="A81" s="55"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="54"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="55"/>
+      <c r="B82" s="48"/>
+      <c r="C82" s="54"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="48"/>
+      <c r="B83" s="48"/>
+      <c r="C83" s="54"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="43"/>
+      <c r="B84" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="46">
-        <f>SUM(C60:C80)</f>
+      <c r="C84" s="46">
+        <f>SUM(C60:C83)</f>
         <v>100750</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6" t="s">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C82" s="47">
-        <f>C59-C81</f>
+      <c r="C85" s="47">
+        <f>C59-C84</f>
         <v>1200</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B87" s="13"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B88" s="13" t="s">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="13"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="13" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B89" s="13" t="s">
+    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B92" s="13" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="2:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="B98" s="13" t="s">
+    <row r="101" spans="2:2" ht="90" x14ac:dyDescent="0.25">
+      <c r="B101" s="13" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="13"/>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B101" s="13"/>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B103" s="13"/>
-    </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B113" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
-        <v>276</v>
-      </c>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="13"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="13"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="13"/>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9873,7 +9972,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6078F90-1BFA-44D9-9906-5A72B5F0645C}">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -10565,67 +10664,95 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="55"/>
+      <c r="A85" s="55">
+        <v>46105</v>
+      </c>
       <c r="B85" s="48"/>
-      <c r="C85" s="54"/>
+      <c r="C85" s="54">
+        <v>5000</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="48"/>
+      <c r="A86" s="55">
+        <v>46141</v>
+      </c>
       <c r="B86" s="48"/>
-      <c r="C86" s="54"/>
+      <c r="C86" s="54">
+        <v>1500</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="43"/>
-      <c r="B87" s="43" t="s">
+      <c r="A87" s="55"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="54"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="55"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="54"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="55"/>
+      <c r="B89" s="48"/>
+      <c r="C89" s="54"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="48"/>
+      <c r="B90" s="48"/>
+      <c r="C90" s="54"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="43"/>
+      <c r="B91" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="C87" s="46">
-        <f>SUM(C75:C86)</f>
-        <v>31400</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6" t="s">
+      <c r="C91" s="46">
+        <f>SUM(C75:C90)</f>
+        <v>37900</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C88" s="47">
-        <f>C74-C87</f>
-        <v>6750</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="B92" s="13" t="s">
+      <c r="C92" s="47">
+        <f>C74-C91</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="B96" s="13" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B93" s="13" t="s">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="13" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="B94" s="13" t="s">
+    <row r="98" spans="2:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B98" s="13" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B95" s="13" t="s">
+    <row r="99" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B99" s="13" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="B96" s="13" t="s">
+    <row r="100" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B100" s="13" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="97" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B97" s="13" t="s">
+    <row r="101" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B101" s="13" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="98" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B98" s="13" t="s">
+    <row r="102" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B102" s="13" t="s">
         <v>317</v>
       </c>
     </row>

--- a/Documents/Actividades realizadas/ActividadesN__.xlsx
+++ b/Documents/Actividades realizadas/ActividadesN__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\1.- VioletaSystem\Documents\Actividades realizadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05570031-43F5-41C0-9EE9-0C95EFAD6C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A39041B-5AE8-4817-B8BD-CB93DE6E5C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20445" yWindow="-12135" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HORAS" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="356">
   <si>
     <t>Descripción</t>
   </si>
@@ -1102,6 +1102,9 @@
   </si>
   <si>
     <t>Modificar el ticket para que muestre el metal del cliente y el metal que da la empresa</t>
+  </si>
+  <si>
+    <t>Rediseño de la pantalla de taller para optimizar el espacio y que todo sea más compacto y mejor, asi como la reunion para llegar a esos acuerdos</t>
   </si>
 </sst>
 </file>
@@ -1559,30 +1562,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="3" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1598,11 +1577,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1938,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K387"/>
+  <dimension ref="A1:K389"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8583,7 +8586,7 @@
     </row>
     <row r="344" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A344" s="5"/>
-      <c r="C344" s="61">
+      <c r="C344" s="9">
         <v>46150</v>
       </c>
       <c r="D344" s="13" t="s">
@@ -8595,13 +8598,13 @@
       <c r="F344" s="2">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H344" s="14">
+      <c r="H344" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="345" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A345" s="5"/>
-      <c r="C345" s="61">
+      <c r="C345" s="9">
         <v>46150</v>
       </c>
       <c r="D345" s="13" t="s">
@@ -8613,226 +8616,235 @@
       <c r="F345" s="2">
         <v>0.52083333333333337</v>
       </c>
-      <c r="H345" s="14">
+      <c r="H345" s="20">
         <v>1.5</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A346" s="5"/>
-      <c r="C346" s="61"/>
-      <c r="D346" s="13"/>
-      <c r="E346" s="2"/>
-      <c r="F346" s="2"/>
+      <c r="C346" s="61">
+        <v>46194</v>
+      </c>
+      <c r="D346" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E346" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F346" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H346" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="5"/>
+      <c r="C347" s="61"/>
+      <c r="D347" s="13"/>
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A348" s="75" t="s">
+      <c r="A348" s="5"/>
+      <c r="C348" s="61"/>
+      <c r="D348" s="13"/>
+      <c r="E348" s="2"/>
+      <c r="F348" s="2"/>
+    </row>
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A349" s="5"/>
+      <c r="E349" s="2"/>
+      <c r="F349" s="2"/>
+    </row>
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A350" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B348" s="75"/>
-      <c r="C348" s="75"/>
-      <c r="D348" s="75"/>
-      <c r="E348" s="75"/>
-      <c r="F348" s="75"/>
-      <c r="G348" s="16">
-        <f>SUM(G2:G347)</f>
+      <c r="B350" s="83"/>
+      <c r="C350" s="83"/>
+      <c r="D350" s="83"/>
+      <c r="E350" s="83"/>
+      <c r="F350" s="83"/>
+      <c r="G350" s="16">
+        <f>SUM(G2:G349)</f>
         <v>314.78999999999996</v>
       </c>
-      <c r="H348" s="16">
-        <f>SUM(H2:H347)</f>
-        <v>198.3</v>
-      </c>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A349" s="75" t="s">
+      <c r="H350" s="16">
+        <f>SUM(H2:H349)</f>
+        <v>208.3</v>
+      </c>
+    </row>
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A351" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="B349" s="75"/>
-      <c r="C349" s="75"/>
-      <c r="D349" s="75"/>
-      <c r="E349" s="75"/>
-      <c r="F349" s="75"/>
-      <c r="G349" s="16">
+      <c r="B351" s="83"/>
+      <c r="C351" s="83"/>
+      <c r="D351" s="83"/>
+      <c r="E351" s="83"/>
+      <c r="F351" s="83"/>
+      <c r="G351" s="16">
         <v>200</v>
       </c>
-      <c r="H349" s="16">
+      <c r="H351" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A350" s="75" t="s">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A352" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="B350" s="75"/>
-      <c r="C350" s="75"/>
-      <c r="D350" s="75"/>
-      <c r="E350" s="75"/>
-      <c r="F350" s="75"/>
-      <c r="G350" s="17">
-        <f>G349*G348</f>
-        <v>62957.999999999993</v>
-      </c>
-      <c r="H350" s="18">
-        <f>H349*H348</f>
-        <v>59490</v>
-      </c>
-      <c r="J350">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="351" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A351" s="75" t="s">
-        <v>58</v>
-      </c>
-      <c r="B351" s="75"/>
-      <c r="C351" s="75"/>
-      <c r="D351" s="75"/>
-      <c r="E351" s="75"/>
-      <c r="F351" s="75"/>
-      <c r="G351" s="80">
-        <f>G350+H350</f>
-        <v>122448</v>
-      </c>
-      <c r="H351" s="80"/>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A352" s="10"/>
-      <c r="B352" s="83" t="s">
-        <v>60</v>
-      </c>
+      <c r="B352" s="83"/>
       <c r="C352" s="83"/>
       <c r="D352" s="83"/>
       <c r="E352" s="83"/>
       <c r="F352" s="83"/>
-      <c r="G352" s="21"/>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A353" s="11">
-        <v>45109</v>
-      </c>
-      <c r="B353" s="84" t="s">
-        <v>59</v>
-      </c>
-      <c r="C353" s="84"/>
-      <c r="D353" s="84"/>
-      <c r="E353" s="84"/>
-      <c r="F353" s="84"/>
-      <c r="G353" s="85">
-        <v>10000</v>
-      </c>
-      <c r="H353" s="85"/>
+      <c r="G352" s="17">
+        <f>G351*G350</f>
+        <v>62957.999999999993</v>
+      </c>
+      <c r="H352" s="18">
+        <f>H351*H350</f>
+        <v>62490</v>
+      </c>
+      <c r="J352">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A353" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="B353" s="83"/>
+      <c r="C353" s="83"/>
+      <c r="D353" s="83"/>
+      <c r="E353" s="83"/>
+      <c r="F353" s="83"/>
+      <c r="G353" s="72">
+        <f>G352+H352</f>
+        <v>125448</v>
+      </c>
+      <c r="H353" s="72"/>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A354" s="11"/>
-      <c r="B354" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C354" s="86"/>
-      <c r="D354" s="86"/>
-      <c r="E354" s="86"/>
-      <c r="F354" s="86"/>
-      <c r="G354" s="85">
-        <v>5000</v>
-      </c>
-      <c r="H354" s="85"/>
+      <c r="A354" s="10"/>
+      <c r="B354" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="C354" s="75"/>
+      <c r="D354" s="75"/>
+      <c r="E354" s="75"/>
+      <c r="F354" s="75"/>
+      <c r="G354" s="21"/>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="11">
-        <v>45278</v>
+        <v>45109</v>
       </c>
       <c r="B355" s="76" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C355" s="76"/>
       <c r="D355" s="76"/>
       <c r="E355" s="76"/>
       <c r="F355" s="76"/>
-      <c r="G355" s="85">
-        <v>9800</v>
-      </c>
-      <c r="H355" s="85"/>
+      <c r="G355" s="78">
+        <v>10000</v>
+      </c>
+      <c r="H355" s="78"/>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="11"/>
-      <c r="B356" s="76"/>
-      <c r="C356" s="76"/>
-      <c r="D356" s="76"/>
-      <c r="E356" s="76"/>
-      <c r="F356" s="76"/>
-      <c r="G356" s="85">
-        <v>78298</v>
-      </c>
-      <c r="H356" s="85"/>
+      <c r="B356" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="C356" s="79"/>
+      <c r="D356" s="79"/>
+      <c r="E356" s="79"/>
+      <c r="F356" s="79"/>
+      <c r="G356" s="78">
+        <v>5000</v>
+      </c>
+      <c r="H356" s="78"/>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A357" s="11"/>
-      <c r="B357" s="76"/>
-      <c r="C357" s="76"/>
-      <c r="D357" s="76"/>
-      <c r="E357" s="76"/>
-      <c r="F357" s="76"/>
-      <c r="G357" s="85"/>
-      <c r="H357" s="85"/>
+      <c r="A357" s="11">
+        <v>45278</v>
+      </c>
+      <c r="B357" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C357" s="77"/>
+      <c r="D357" s="77"/>
+      <c r="E357" s="77"/>
+      <c r="F357" s="77"/>
+      <c r="G357" s="78">
+        <v>9800</v>
+      </c>
+      <c r="H357" s="78"/>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="11"/>
-      <c r="B358" s="76"/>
-      <c r="C358" s="76"/>
-      <c r="D358" s="76"/>
-      <c r="E358" s="76"/>
-      <c r="F358" s="76"/>
-      <c r="G358" s="85"/>
-      <c r="H358" s="85"/>
+      <c r="B358" s="77"/>
+      <c r="C358" s="77"/>
+      <c r="D358" s="77"/>
+      <c r="E358" s="77"/>
+      <c r="F358" s="77"/>
+      <c r="G358" s="78">
+        <v>78298</v>
+      </c>
+      <c r="H358" s="78"/>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="11"/>
-      <c r="B359" s="76" t="s">
-        <v>62</v>
-      </c>
-      <c r="C359" s="76"/>
-      <c r="D359" s="76"/>
-      <c r="E359" s="76"/>
-      <c r="F359" s="76"/>
-      <c r="G359" s="85">
-        <f>SUM(G353:H358)</f>
-        <v>103098</v>
-      </c>
-      <c r="H359" s="85"/>
-    </row>
-    <row r="360" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A360" s="81" t="s">
-        <v>61</v>
-      </c>
-      <c r="B360" s="81"/>
-      <c r="C360" s="81"/>
-      <c r="D360" s="81"/>
-      <c r="E360" s="81"/>
-      <c r="F360" s="81"/>
-      <c r="G360" s="82">
-        <f>G351-G359</f>
-        <v>19350</v>
-      </c>
-      <c r="H360" s="82"/>
+      <c r="B359" s="77"/>
+      <c r="C359" s="77"/>
+      <c r="D359" s="77"/>
+      <c r="E359" s="77"/>
+      <c r="F359" s="77"/>
+      <c r="G359" s="78"/>
+      <c r="H359" s="78"/>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A360" s="11"/>
+      <c r="B360" s="77"/>
+      <c r="C360" s="77"/>
+      <c r="D360" s="77"/>
+      <c r="E360" s="77"/>
+      <c r="F360" s="77"/>
+      <c r="G360" s="78"/>
+      <c r="H360" s="78"/>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="11"/>
-      <c r="B361" s="12"/>
-      <c r="C361" s="12"/>
-      <c r="D361" s="12"/>
-      <c r="E361" s="12"/>
-      <c r="F361" s="12"/>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A362" s="11"/>
-      <c r="B362" s="12"/>
-      <c r="C362" s="12"/>
-      <c r="D362" s="12"/>
-      <c r="E362" s="12"/>
-      <c r="F362" s="12"/>
+      <c r="B361" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="C361" s="77"/>
+      <c r="D361" s="77"/>
+      <c r="E361" s="77"/>
+      <c r="F361" s="77"/>
+      <c r="G361" s="78">
+        <f>SUM(G355:H360)</f>
+        <v>103098</v>
+      </c>
+      <c r="H361" s="78"/>
+    </row>
+    <row r="362" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A362" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B362" s="73"/>
+      <c r="C362" s="73"/>
+      <c r="D362" s="73"/>
+      <c r="E362" s="73"/>
+      <c r="F362" s="73"/>
+      <c r="G362" s="74">
+        <f>G353-G361</f>
+        <v>22350</v>
+      </c>
+      <c r="H362" s="74"/>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="11"/>
@@ -8963,190 +8975,206 @@
       <c r="F378" s="12"/>
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A379" s="9"/>
-      <c r="B379" s="77" t="s">
+      <c r="A379" s="11"/>
+      <c r="B379" s="12"/>
+      <c r="C379" s="12"/>
+      <c r="D379" s="12"/>
+      <c r="E379" s="12"/>
+      <c r="F379" s="12"/>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A380" s="11"/>
+      <c r="B380" s="12"/>
+      <c r="C380" s="12"/>
+      <c r="D380" s="12"/>
+      <c r="E380" s="12"/>
+      <c r="F380" s="12"/>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A381" s="9"/>
+      <c r="B381" s="84" t="s">
         <v>56</v>
       </c>
-      <c r="C379" s="77"/>
-      <c r="D379" s="77"/>
-      <c r="E379" s="77"/>
-      <c r="F379" s="77"/>
-      <c r="G379" s="20"/>
-      <c r="H379" s="20"/>
-      <c r="I379" s="7">
-        <f>G348+H348</f>
-        <v>513.08999999999992</v>
-      </c>
-      <c r="J379" s="7">
-        <f>I379</f>
-        <v>513.08999999999992</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A380" s="5"/>
-      <c r="B380" s="78" t="s">
+      <c r="C381" s="84"/>
+      <c r="D381" s="84"/>
+      <c r="E381" s="84"/>
+      <c r="F381" s="84"/>
+      <c r="G381" s="20"/>
+      <c r="H381" s="20"/>
+      <c r="I381" s="7">
+        <f>G350+H350</f>
+        <v>523.08999999999992</v>
+      </c>
+      <c r="J381" s="7">
+        <f>I381</f>
+        <v>523.08999999999992</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A382" s="5"/>
+      <c r="B382" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="C380" s="78"/>
-      <c r="D380" s="78"/>
-      <c r="E380" s="78"/>
-      <c r="F380" s="78"/>
-      <c r="I380" s="7">
+      <c r="C382" s="85"/>
+      <c r="D382" s="85"/>
+      <c r="E382" s="85"/>
+      <c r="F382" s="85"/>
+      <c r="I382" s="7">
         <v>300</v>
       </c>
-      <c r="J380" s="7">
+      <c r="J382" s="7">
         <v>200</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A381" s="5"/>
-      <c r="B381" s="78" t="s">
+    <row r="383" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A383" s="5"/>
+      <c r="B383" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="C381" s="78"/>
-      <c r="D381" s="78"/>
-      <c r="E381" s="78"/>
-      <c r="F381" s="78"/>
-      <c r="I381" s="8">
-        <f>I380*I379</f>
-        <v>153926.99999999997</v>
-      </c>
-      <c r="J381" s="8">
-        <f>J380*J379</f>
-        <v>102617.99999999999</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A382" s="22"/>
-      <c r="B382" s="79" t="s">
+      <c r="C383" s="85"/>
+      <c r="D383" s="85"/>
+      <c r="E383" s="85"/>
+      <c r="F383" s="85"/>
+      <c r="I383" s="8">
+        <f>I382*I381</f>
+        <v>156926.99999999997</v>
+      </c>
+      <c r="J383" s="8">
+        <f>J382*J381</f>
+        <v>104617.99999999999</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A384" s="22"/>
+      <c r="B384" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="C382" s="79"/>
-      <c r="D382" s="79"/>
-      <c r="E382" s="79"/>
-      <c r="F382" s="79"/>
-      <c r="G382" s="23"/>
-      <c r="H382" s="23"/>
-      <c r="I382" s="24"/>
-      <c r="J382" s="24"/>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A383" s="25">
+      <c r="C384" s="86"/>
+      <c r="D384" s="86"/>
+      <c r="E384" s="86"/>
+      <c r="F384" s="86"/>
+      <c r="G384" s="23"/>
+      <c r="H384" s="23"/>
+      <c r="I384" s="24"/>
+      <c r="J384" s="24"/>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A385" s="25">
         <v>45109</v>
       </c>
-      <c r="B383" s="73" t="s">
+      <c r="B385" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="C383" s="73"/>
-      <c r="D383" s="73"/>
-      <c r="E383" s="73"/>
-      <c r="F383" s="73"/>
-      <c r="G383" s="26"/>
-      <c r="H383" s="26"/>
-      <c r="I383" s="27">
-        <v>10000</v>
-      </c>
-      <c r="J383" s="27">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A384" s="25"/>
-      <c r="B384" s="28"/>
-      <c r="C384" s="28"/>
-      <c r="D384" s="28"/>
-      <c r="E384" s="28"/>
-      <c r="F384" s="28"/>
-      <c r="G384" s="26"/>
-      <c r="H384" s="26"/>
-      <c r="I384" s="29"/>
-      <c r="J384" s="29"/>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A385" s="25"/>
-      <c r="B385" s="28"/>
-      <c r="C385" s="28"/>
-      <c r="D385" s="28"/>
-      <c r="E385" s="28"/>
-      <c r="F385" s="28"/>
+      <c r="C385" s="81"/>
+      <c r="D385" s="81"/>
+      <c r="E385" s="81"/>
+      <c r="F385" s="81"/>
       <c r="G385" s="26"/>
       <c r="H385" s="26"/>
-      <c r="I385" s="29"/>
-      <c r="J385" s="29"/>
-    </row>
-    <row r="386" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="I385" s="27">
+        <v>10000</v>
+      </c>
+      <c r="J385" s="27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" s="25"/>
-      <c r="B386" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="C386" s="74"/>
-      <c r="D386" s="74"/>
-      <c r="E386" s="74"/>
-      <c r="F386" s="74"/>
+      <c r="B386" s="28"/>
+      <c r="C386" s="28"/>
+      <c r="D386" s="28"/>
+      <c r="E386" s="28"/>
+      <c r="F386" s="28"/>
       <c r="G386" s="26"/>
       <c r="H386" s="26"/>
-      <c r="I386" s="30">
-        <f>SUM(I383:I385)</f>
+      <c r="I386" s="29"/>
+      <c r="J386" s="29"/>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A387" s="25"/>
+      <c r="B387" s="28"/>
+      <c r="C387" s="28"/>
+      <c r="D387" s="28"/>
+      <c r="E387" s="28"/>
+      <c r="F387" s="28"/>
+      <c r="G387" s="26"/>
+      <c r="H387" s="26"/>
+      <c r="I387" s="29"/>
+      <c r="J387" s="29"/>
+    </row>
+    <row r="388" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A388" s="25"/>
+      <c r="B388" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="C388" s="82"/>
+      <c r="D388" s="82"/>
+      <c r="E388" s="82"/>
+      <c r="F388" s="82"/>
+      <c r="G388" s="26"/>
+      <c r="H388" s="26"/>
+      <c r="I388" s="30">
+        <f>SUM(I385:I387)</f>
         <v>10000</v>
       </c>
-      <c r="J386" s="30">
-        <f>SUM(J383:J385)</f>
+      <c r="J388" s="30">
+        <f>SUM(J385:J387)</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="387" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A387" s="31">
+    <row r="389" spans="1:10" ht="33.75" x14ac:dyDescent="0.5">
+      <c r="A389" s="31">
         <v>45109</v>
       </c>
-      <c r="B387" s="72" t="s">
+      <c r="B389" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="C387" s="72"/>
-      <c r="D387" s="72"/>
-      <c r="E387" s="72"/>
-      <c r="F387" s="72"/>
-      <c r="G387" s="32"/>
-      <c r="H387" s="32"/>
-      <c r="I387" s="33">
-        <f>I381-I386</f>
-        <v>143926.99999999997</v>
-      </c>
-      <c r="J387" s="33">
-        <f>J381-J386</f>
-        <v>92617.999999999985</v>
+      <c r="C389" s="80"/>
+      <c r="D389" s="80"/>
+      <c r="E389" s="80"/>
+      <c r="F389" s="80"/>
+      <c r="G389" s="32"/>
+      <c r="H389" s="32"/>
+      <c r="I389" s="33">
+        <f>I383-I388</f>
+        <v>146926.99999999997</v>
+      </c>
+      <c r="J389" s="33">
+        <f>J383-J388</f>
+        <v>94617.999999999985</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="G351:H351"/>
-    <mergeCell ref="A360:F360"/>
-    <mergeCell ref="G360:H360"/>
-    <mergeCell ref="B352:F352"/>
-    <mergeCell ref="B353:F353"/>
+    <mergeCell ref="B389:F389"/>
+    <mergeCell ref="B385:F385"/>
+    <mergeCell ref="B388:F388"/>
+    <mergeCell ref="A351:F351"/>
+    <mergeCell ref="A350:F350"/>
+    <mergeCell ref="A352:F352"/>
+    <mergeCell ref="A353:F353"/>
     <mergeCell ref="B359:F359"/>
-    <mergeCell ref="G353:H353"/>
-    <mergeCell ref="G354:H354"/>
-    <mergeCell ref="G359:H359"/>
-    <mergeCell ref="G356:H356"/>
-    <mergeCell ref="G357:H357"/>
-    <mergeCell ref="G358:H358"/>
-    <mergeCell ref="G355:H355"/>
-    <mergeCell ref="B355:F355"/>
-    <mergeCell ref="B354:F354"/>
-    <mergeCell ref="B356:F356"/>
-    <mergeCell ref="B387:F387"/>
-    <mergeCell ref="B383:F383"/>
-    <mergeCell ref="B386:F386"/>
-    <mergeCell ref="A349:F349"/>
-    <mergeCell ref="A348:F348"/>
-    <mergeCell ref="A350:F350"/>
-    <mergeCell ref="A351:F351"/>
-    <mergeCell ref="B357:F357"/>
-    <mergeCell ref="B358:F358"/>
-    <mergeCell ref="B379:F379"/>
-    <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B360:F360"/>
     <mergeCell ref="B381:F381"/>
     <mergeCell ref="B382:F382"/>
+    <mergeCell ref="B383:F383"/>
+    <mergeCell ref="B384:F384"/>
+    <mergeCell ref="G353:H353"/>
+    <mergeCell ref="A362:F362"/>
+    <mergeCell ref="G362:H362"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B355:F355"/>
+    <mergeCell ref="B361:F361"/>
+    <mergeCell ref="G355:H355"/>
+    <mergeCell ref="G356:H356"/>
+    <mergeCell ref="G361:H361"/>
+    <mergeCell ref="G358:H358"/>
+    <mergeCell ref="G359:H359"/>
+    <mergeCell ref="G360:H360"/>
+    <mergeCell ref="G357:H357"/>
+    <mergeCell ref="B357:F357"/>
+    <mergeCell ref="B356:F356"/>
+    <mergeCell ref="B358:F358"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -10542,10 +10570,14 @@
       </c>
       <c r="C70" s="88"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="48"/>
-      <c r="B71" s="62"/>
-      <c r="C71" s="63"/>
+      <c r="B71" s="62" t="s">
+        <v>355</v>
+      </c>
+      <c r="C71" s="63">
+        <v>3000</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="48"/>
@@ -10564,7 +10596,7 @@
       </c>
       <c r="C74" s="46">
         <f>SUM(C2:C73)</f>
-        <v>38150</v>
+        <v>41150</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10718,7 +10750,7 @@
       </c>
       <c r="C92" s="47">
         <f>C74-C91</f>
-        <v>250</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
